--- a/assets/data/ine/excel/ove_ine_venezuela_indice_hojas.xlsx
+++ b/assets/data/ine/excel/ove_ine_venezuela_indice_hojas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="indice_hojas" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metadatos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="indice_hojas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="metadatos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -88,11 +88,79 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -107,13 +175,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -122,7 +190,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -137,13 +205,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>

--- a/assets/data/ine/excel/ove_ine_venezuela_indice_hojas.xlsx
+++ b/assets/data/ine/excel/ove_ine_venezuela_indice_hojas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="indice_hojas" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="metadatos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="indice_hojas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metadatos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="[$-es-ES]#,##0"/>
+  </numFmts>
   <fonts count="5">
     <font>
       <name val="Calibri"/>
@@ -69,7 +71,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -83,84 +85,19 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -175,13 +112,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -190,7 +130,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -205,13 +145,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -629,13 +572,13 @@
           <t>Por Variables</t>
         </is>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="G7" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="H7" s="4" t="n">
+      <c r="H7" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="I7" s="4" t="n">
+      <c r="I7" s="7" t="n">
         <v>204</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -676,13 +619,13 @@
           <t>Pobres y Extremos</t>
         </is>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G8" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="H8" s="4" t="n">
+      <c r="H8" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="I8" s="4" t="n">
+      <c r="I8" s="7" t="n">
         <v>186</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -723,13 +666,13 @@
           <t>Por Vriables</t>
         </is>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="G9" s="7" t="n">
         <v>63</v>
       </c>
-      <c r="H9" s="4" t="n">
+      <c r="H9" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="I9" s="4" t="n">
+      <c r="I9" s="7" t="n">
         <v>512</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -770,13 +713,13 @@
           <t>Pobres y Extremos</t>
         </is>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="G10" s="7" t="n">
         <v>63</v>
       </c>
-      <c r="H10" s="4" t="n">
+      <c r="H10" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="I10" s="4" t="n">
+      <c r="I10" s="7" t="n">
         <v>466</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -817,13 +760,13 @@
           <t>Por Variables</t>
         </is>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="G11" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="H11" s="4" t="n">
+      <c r="H11" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="I11" s="4" t="n">
+      <c r="I11" s="7" t="n">
         <v>204</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -864,13 +807,13 @@
           <t>Pobres y Extremos</t>
         </is>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="G12" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="H12" s="4" t="n">
+      <c r="H12" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="I12" s="4" t="n">
+      <c r="I12" s="7" t="n">
         <v>186</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -911,13 +854,13 @@
           <t>Por Variables</t>
         </is>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="G13" s="7" t="n">
         <v>57</v>
       </c>
-      <c r="H13" s="4" t="n">
+      <c r="H13" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="I13" s="4" t="n">
+      <c r="I13" s="7" t="n">
         <v>446</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -958,13 +901,13 @@
           <t>Pobres y Extremos</t>
         </is>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="G14" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="H14" s="4" t="n">
+      <c r="H14" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="I14" s="4" t="n">
+      <c r="I14" s="7" t="n">
         <v>286</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1005,13 +948,13 @@
           <t>Por Variables</t>
         </is>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="G15" s="7" t="n">
         <v>43</v>
       </c>
-      <c r="H15" s="4" t="n">
+      <c r="H15" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="I15" s="4" t="n">
+      <c r="I15" s="7" t="n">
         <v>292</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1052,13 +995,13 @@
           <t>Pobres y Extremos</t>
         </is>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="G16" s="7" t="n">
         <v>43</v>
       </c>
-      <c r="H16" s="4" t="n">
+      <c r="H16" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="I16" s="4" t="n">
+      <c r="I16" s="7" t="n">
         <v>266</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1099,13 +1042,13 @@
           <t>Por Variables</t>
         </is>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="G17" s="7" t="n">
         <v>49</v>
       </c>
-      <c r="H17" s="4" t="n">
+      <c r="H17" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="I17" s="4" t="n">
+      <c r="I17" s="7" t="n">
         <v>358</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1146,13 +1089,13 @@
           <t>Pobres y Extremos</t>
         </is>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="G18" s="7" t="n">
         <v>49</v>
       </c>
-      <c r="H18" s="4" t="n">
+      <c r="H18" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="I18" s="4" t="n">
+      <c r="I18" s="7" t="n">
         <v>326</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1193,13 +1136,13 @@
           <t>Por Variables</t>
         </is>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="G19" s="7" t="n">
         <v>39</v>
       </c>
-      <c r="H19" s="4" t="n">
+      <c r="H19" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="I19" s="4" t="n">
+      <c r="I19" s="7" t="n">
         <v>248</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1240,13 +1183,13 @@
           <t>Pobres y Extremos</t>
         </is>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="G20" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="H20" s="4" t="n">
+      <c r="H20" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="I20" s="4" t="n">
+      <c r="I20" s="7" t="n">
         <v>226</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1287,13 +1230,13 @@
           <t>Por Variables</t>
         </is>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="G21" s="7" t="n">
         <v>29</v>
       </c>
-      <c r="H21" s="4" t="n">
+      <c r="H21" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="I21" s="4" t="n">
+      <c r="I21" s="7" t="n">
         <v>138</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -1334,13 +1277,13 @@
           <t>Pobres y Extremos</t>
         </is>
       </c>
-      <c r="G22" s="4" t="n">
+      <c r="G22" s="7" t="n">
         <v>29</v>
       </c>
-      <c r="H22" s="4" t="n">
+      <c r="H22" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="I22" s="4" t="n">
+      <c r="I22" s="7" t="n">
         <v>126</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -1381,13 +1324,13 @@
           <t>Por Variables</t>
         </is>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="G23" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="H23" s="4" t="n">
+      <c r="H23" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="I23" s="4" t="n">
+      <c r="I23" s="7" t="n">
         <v>116</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -1428,13 +1371,13 @@
           <t>Pobres y Extremos</t>
         </is>
       </c>
-      <c r="G24" s="4" t="n">
+      <c r="G24" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="H24" s="4" t="n">
+      <c r="H24" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="I24" s="4" t="n">
+      <c r="I24" s="7" t="n">
         <v>106</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -1475,13 +1418,13 @@
           <t>Por Variables</t>
         </is>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="G25" s="7" t="n">
         <v>64</v>
       </c>
-      <c r="H25" s="4" t="n">
+      <c r="H25" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="I25" s="4" t="n">
+      <c r="I25" s="7" t="n">
         <v>534</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -1522,13 +1465,13 @@
           <t>POBREZA</t>
         </is>
       </c>
-      <c r="G26" s="4" t="n">
+      <c r="G26" s="7" t="n">
         <v>65</v>
       </c>
-      <c r="H26" s="4" t="n">
+      <c r="H26" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="I26" s="4" t="n">
+      <c r="I26" s="7" t="n">
         <v>486</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -1569,13 +1512,13 @@
           <t>Por Variables</t>
         </is>
       </c>
-      <c r="G27" s="4" t="n">
+      <c r="G27" s="7" t="n">
         <v>71</v>
       </c>
-      <c r="H27" s="4" t="n">
+      <c r="H27" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="I27" s="4" t="n">
+      <c r="I27" s="7" t="n">
         <v>600</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -1616,13 +1559,13 @@
           <t>Pobres y Extremos</t>
         </is>
       </c>
-      <c r="G28" s="4" t="n">
+      <c r="G28" s="7" t="n">
         <v>73</v>
       </c>
-      <c r="H28" s="4" t="n">
+      <c r="H28" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="I28" s="4" t="n">
+      <c r="I28" s="7" t="n">
         <v>546</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -1663,13 +1606,13 @@
           <t>Por Variables</t>
         </is>
       </c>
-      <c r="G29" s="4" t="n">
+      <c r="G29" s="7" t="n">
         <v>51</v>
       </c>
-      <c r="H29" s="4" t="n">
+      <c r="H29" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="I29" s="4" t="n">
+      <c r="I29" s="7" t="n">
         <v>380</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -1710,13 +1653,13 @@
           <t>Pobres y Extremos</t>
         </is>
       </c>
-      <c r="G30" s="4" t="n">
+      <c r="G30" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="H30" s="4" t="n">
+      <c r="H30" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="I30" s="4" t="n">
+      <c r="I30" s="7" t="n">
         <v>346</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -1757,13 +1700,13 @@
           <t>Por Variables</t>
         </is>
       </c>
-      <c r="G31" s="4" t="n">
+      <c r="G31" s="7" t="n">
         <v>44</v>
       </c>
-      <c r="H31" s="4" t="n">
+      <c r="H31" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="I31" s="4" t="n">
+      <c r="I31" s="7" t="n">
         <v>292</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -1804,13 +1747,13 @@
           <t>Pobres y Extremos</t>
         </is>
       </c>
-      <c r="G32" s="4" t="n">
+      <c r="G32" s="7" t="n">
         <v>44</v>
       </c>
-      <c r="H32" s="4" t="n">
+      <c r="H32" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="I32" s="4" t="n">
+      <c r="I32" s="7" t="n">
         <v>266</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -1851,13 +1794,13 @@
           <t>Por Variables</t>
         </is>
       </c>
-      <c r="G33" s="4" t="n">
+      <c r="G33" s="7" t="n">
         <v>39</v>
       </c>
-      <c r="H33" s="4" t="n">
+      <c r="H33" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="I33" s="4" t="n">
+      <c r="I33" s="7" t="n">
         <v>248</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -1898,13 +1841,13 @@
           <t>Pobres y Extremos</t>
         </is>
       </c>
-      <c r="G34" s="4" t="n">
+      <c r="G34" s="7" t="n">
         <v>39</v>
       </c>
-      <c r="H34" s="4" t="n">
+      <c r="H34" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="I34" s="4" t="n">
+      <c r="I34" s="7" t="n">
         <v>226</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -1945,13 +1888,13 @@
           <t xml:space="preserve">Por Variables </t>
         </is>
       </c>
-      <c r="G35" s="4" t="n">
+      <c r="G35" s="7" t="n">
         <v>63</v>
       </c>
-      <c r="H35" s="4" t="n">
+      <c r="H35" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="I35" s="4" t="n">
+      <c r="I35" s="7" t="n">
         <v>512</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -1992,13 +1935,13 @@
           <t>Pobres y Extremos</t>
         </is>
       </c>
-      <c r="G36" s="4" t="n">
+      <c r="G36" s="7" t="n">
         <v>63</v>
       </c>
-      <c r="H36" s="4" t="n">
+      <c r="H36" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="I36" s="4" t="n">
+      <c r="I36" s="7" t="n">
         <v>466</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
@@ -2039,13 +1982,13 @@
           <t>Por Variables</t>
         </is>
       </c>
-      <c r="G37" s="4" t="n">
+      <c r="G37" s="7" t="n">
         <v>47</v>
       </c>
-      <c r="H37" s="4" t="n">
+      <c r="H37" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="I37" s="4" t="n">
+      <c r="I37" s="7" t="n">
         <v>336</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -2086,13 +2029,13 @@
           <t>Pobres y Extremos</t>
         </is>
       </c>
-      <c r="G38" s="4" t="n">
+      <c r="G38" s="7" t="n">
         <v>47</v>
       </c>
-      <c r="H38" s="4" t="n">
+      <c r="H38" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="I38" s="4" t="n">
+      <c r="I38" s="7" t="n">
         <v>306</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
@@ -2133,13 +2076,13 @@
           <t>Por Variables</t>
         </is>
       </c>
-      <c r="G39" s="4" t="n">
+      <c r="G39" s="7" t="n">
         <v>67</v>
       </c>
-      <c r="H39" s="4" t="n">
+      <c r="H39" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="I39" s="4" t="n">
+      <c r="I39" s="7" t="n">
         <v>556</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -2180,13 +2123,13 @@
           <t>Pobres y Extremos</t>
         </is>
       </c>
-      <c r="G40" s="4" t="n">
+      <c r="G40" s="7" t="n">
         <v>66</v>
       </c>
-      <c r="H40" s="4" t="n">
+      <c r="H40" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="I40" s="4" t="n">
+      <c r="I40" s="7" t="n">
         <v>506</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
@@ -2227,13 +2170,13 @@
           <t>Variables</t>
         </is>
       </c>
-      <c r="G41" s="4" t="n">
+      <c r="G41" s="7" t="n">
         <v>77</v>
       </c>
-      <c r="H41" s="4" t="n">
+      <c r="H41" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="I41" s="4" t="n">
+      <c r="I41" s="7" t="n">
         <v>602</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
@@ -2274,13 +2217,13 @@
           <t>Pobres</t>
         </is>
       </c>
-      <c r="G42" s="4" t="n">
+      <c r="G42" s="7" t="n">
         <v>74</v>
       </c>
-      <c r="H42" s="4" t="n">
+      <c r="H42" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="I42" s="4" t="n">
+      <c r="I42" s="7" t="n">
         <v>548</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
@@ -2321,13 +2264,13 @@
           <t>Pobres y Extremos</t>
         </is>
       </c>
-      <c r="G43" s="4" t="n">
+      <c r="G43" s="7" t="n">
         <v>43</v>
       </c>
-      <c r="H43" s="4" t="n">
+      <c r="H43" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="I43" s="4" t="n">
+      <c r="I43" s="7" t="n">
         <v>266</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
@@ -2368,13 +2311,13 @@
           <t>Por Variables</t>
         </is>
       </c>
-      <c r="G44" s="4" t="n">
+      <c r="G44" s="7" t="n">
         <v>44</v>
       </c>
-      <c r="H44" s="4" t="n">
+      <c r="H44" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="I44" s="4" t="n">
+      <c r="I44" s="7" t="n">
         <v>292</v>
       </c>
       <c r="J44" s="4" t="inlineStr">
@@ -2415,13 +2358,13 @@
           <t>Pobres y Extremos</t>
         </is>
       </c>
-      <c r="G45" s="4" t="n">
+      <c r="G45" s="7" t="n">
         <v>49</v>
       </c>
-      <c r="H45" s="4" t="n">
+      <c r="H45" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="I45" s="4" t="n">
+      <c r="I45" s="7" t="n">
         <v>326</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
@@ -2462,13 +2405,13 @@
           <t>Por variables</t>
         </is>
       </c>
-      <c r="G46" s="4" t="n">
+      <c r="G46" s="7" t="n">
         <v>49</v>
       </c>
-      <c r="H46" s="4" t="n">
+      <c r="H46" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="I46" s="4" t="n">
+      <c r="I46" s="7" t="n">
         <v>358</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
@@ -2509,13 +2452,13 @@
           <t>Por Variables</t>
         </is>
       </c>
-      <c r="G47" s="4" t="n">
+      <c r="G47" s="7" t="n">
         <v>51</v>
       </c>
-      <c r="H47" s="4" t="n">
+      <c r="H47" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="I47" s="4" t="n">
+      <c r="I47" s="7" t="n">
         <v>380</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
@@ -2556,13 +2499,13 @@
           <t>Pobres y Extremos</t>
         </is>
       </c>
-      <c r="G48" s="4" t="n">
+      <c r="G48" s="7" t="n">
         <v>51</v>
       </c>
-      <c r="H48" s="4" t="n">
+      <c r="H48" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="I48" s="4" t="n">
+      <c r="I48" s="7" t="n">
         <v>346</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
@@ -2603,13 +2546,13 @@
           <t>Por Variables</t>
         </is>
       </c>
-      <c r="G49" s="4" t="n">
+      <c r="G49" s="7" t="n">
         <v>61</v>
       </c>
-      <c r="H49" s="4" t="n">
+      <c r="H49" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="I49" s="4" t="n">
+      <c r="I49" s="7" t="n">
         <v>490</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
@@ -2650,13 +2593,13 @@
           <t>Pobres y Extremos</t>
         </is>
       </c>
-      <c r="G50" s="4" t="n">
+      <c r="G50" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="H50" s="4" t="n">
+      <c r="H50" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="I50" s="4" t="n">
+      <c r="I50" s="7" t="n">
         <v>446</v>
       </c>
       <c r="J50" s="4" t="inlineStr">
@@ -2697,13 +2640,13 @@
           <t>Por Variables</t>
         </is>
       </c>
-      <c r="G51" s="4" t="n">
+      <c r="G51" s="7" t="n">
         <v>78</v>
       </c>
-      <c r="H51" s="4" t="n">
+      <c r="H51" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="I51" s="4" t="n">
+      <c r="I51" s="7" t="n">
         <v>688</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
@@ -2744,13 +2687,13 @@
           <t>Pobres y Extremos</t>
         </is>
       </c>
-      <c r="G52" s="4" t="n">
+      <c r="G52" s="7" t="n">
         <v>79</v>
       </c>
-      <c r="H52" s="4" t="n">
+      <c r="H52" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="I52" s="4" t="n">
+      <c r="I52" s="7" t="n">
         <v>626</v>
       </c>
       <c r="J52" s="4" t="inlineStr">
@@ -2791,13 +2734,13 @@
           <t>Pobres y Extremos</t>
         </is>
       </c>
-      <c r="G53" s="4" t="n">
+      <c r="G53" s="7" t="n">
         <v>48</v>
       </c>
-      <c r="H53" s="4" t="n">
+      <c r="H53" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="I53" s="4" t="n">
+      <c r="I53" s="7" t="n">
         <v>326</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
@@ -2838,13 +2781,13 @@
           <t>Por Variables</t>
         </is>
       </c>
-      <c r="G54" s="4" t="n">
+      <c r="G54" s="7" t="n">
         <v>49</v>
       </c>
-      <c r="H54" s="4" t="n">
+      <c r="H54" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="I54" s="4" t="n">
+      <c r="I54" s="7" t="n">
         <v>358</v>
       </c>
       <c r="J54" s="4" t="inlineStr">
@@ -2885,13 +2828,13 @@
           <t>Por Variables</t>
         </is>
       </c>
-      <c r="G55" s="4" t="n">
+      <c r="G55" s="7" t="n">
         <v>63</v>
       </c>
-      <c r="H55" s="4" t="n">
+      <c r="H55" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="I55" s="4" t="n">
+      <c r="I55" s="7" t="n">
         <v>512</v>
       </c>
       <c r="J55" s="4" t="inlineStr">
@@ -2932,13 +2875,13 @@
           <t>Pobres y Extremos</t>
         </is>
       </c>
-      <c r="G56" s="4" t="n">
+      <c r="G56" s="7" t="n">
         <v>63</v>
       </c>
-      <c r="H56" s="4" t="n">
+      <c r="H56" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="I56" s="4" t="n">
+      <c r="I56" s="7" t="n">
         <v>466</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
@@ -2979,13 +2922,13 @@
           <t>Servicio de Agua</t>
         </is>
       </c>
-      <c r="G57" s="4" t="n">
+      <c r="G57" s="7" t="n">
         <v>1137</v>
       </c>
-      <c r="H57" s="4" t="n">
+      <c r="H57" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="I57" s="4" t="n">
+      <c r="I57" s="7" t="n">
         <v>15820</v>
       </c>
       <c r="J57" s="4" t="inlineStr">
@@ -3026,13 +2969,13 @@
           <t>Población Indígena</t>
         </is>
       </c>
-      <c r="G58" s="4" t="n">
+      <c r="G58" s="7" t="n">
         <v>85</v>
       </c>
-      <c r="H58" s="4" t="n">
+      <c r="H58" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="I58" s="4" t="n">
+      <c r="I58" s="7" t="n">
         <v>387</v>
       </c>
       <c r="J58" s="4" t="inlineStr">
@@ -3073,13 +3016,13 @@
           <t>Servicio de Basura</t>
         </is>
       </c>
-      <c r="G59" s="4" t="n">
+      <c r="G59" s="7" t="n">
         <v>1137</v>
       </c>
-      <c r="H59" s="4" t="n">
+      <c r="H59" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="I59" s="4" t="n">
+      <c r="I59" s="7" t="n">
         <v>12430</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
@@ -3120,13 +3063,13 @@
           <t>Población Indígena</t>
         </is>
       </c>
-      <c r="G60" s="4" t="n">
+      <c r="G60" s="7" t="n">
         <v>160</v>
       </c>
-      <c r="H60" s="4" t="n">
+      <c r="H60" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="I60" s="4" t="n">
+      <c r="I60" s="7" t="n">
         <v>763</v>
       </c>
       <c r="J60" s="4" t="inlineStr">
@@ -3167,13 +3110,13 @@
           <t>Eliminación de Excretas</t>
         </is>
       </c>
-      <c r="G61" s="4" t="n">
+      <c r="G61" s="7" t="n">
         <v>1137</v>
       </c>
-      <c r="H61" s="4" t="n">
+      <c r="H61" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="I61" s="4" t="n">
+      <c r="I61" s="7" t="n">
         <v>11300</v>
       </c>
       <c r="J61" s="4" t="inlineStr">
@@ -3214,13 +3157,13 @@
           <t>Servicio Eléctrico</t>
         </is>
       </c>
-      <c r="G62" s="4" t="n">
+      <c r="G62" s="7" t="n">
         <v>1137</v>
       </c>
-      <c r="H62" s="4" t="n">
+      <c r="H62" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="I62" s="4" t="n">
+      <c r="I62" s="7" t="n">
         <v>12430</v>
       </c>
       <c r="J62" s="4" t="inlineStr">
@@ -3261,13 +3204,13 @@
           <t>Frecuencia Servicio Agua</t>
         </is>
       </c>
-      <c r="G63" s="4" t="n">
+      <c r="G63" s="7" t="n">
         <v>1137</v>
       </c>
-      <c r="H63" s="4" t="n">
+      <c r="H63" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="I63" s="4" t="n">
+      <c r="I63" s="7" t="n">
         <v>10170</v>
       </c>
       <c r="J63" s="4" t="inlineStr">
@@ -3308,13 +3251,13 @@
           <t>Frecuencia Servicio Basura</t>
         </is>
       </c>
-      <c r="G64" s="4" t="n">
+      <c r="G64" s="7" t="n">
         <v>1137</v>
       </c>
-      <c r="H64" s="4" t="n">
+      <c r="H64" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="I64" s="4" t="n">
+      <c r="I64" s="7" t="n">
         <v>10170</v>
       </c>
       <c r="J64" s="4" t="inlineStr">
@@ -3355,13 +3298,13 @@
           <t>Gas Directo</t>
         </is>
       </c>
-      <c r="G65" s="4" t="n">
+      <c r="G65" s="7" t="n">
         <v>1137</v>
       </c>
-      <c r="H65" s="4" t="n">
+      <c r="H65" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="I65" s="4" t="n">
+      <c r="I65" s="7" t="n">
         <v>7910</v>
       </c>
       <c r="J65" s="4" t="inlineStr">
@@ -3402,13 +3345,13 @@
           <t>Población Indígena</t>
         </is>
       </c>
-      <c r="G66" s="4" t="n">
+      <c r="G66" s="7" t="n">
         <v>535</v>
       </c>
-      <c r="H66" s="4" t="n">
+      <c r="H66" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="I66" s="4" t="n">
+      <c r="I66" s="7" t="n">
         <v>2637</v>
       </c>
       <c r="J66" s="4" t="inlineStr">
@@ -3449,13 +3392,13 @@
           <t>Población Indígena</t>
         </is>
       </c>
-      <c r="G67" s="4" t="n">
+      <c r="G67" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="H67" s="4" t="n">
+      <c r="H67" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="I67" s="4" t="n">
+      <c r="I67" s="7" t="n">
         <v>165</v>
       </c>
       <c r="J67" s="4" t="inlineStr">
@@ -3496,13 +3439,13 @@
           <t>Población Indígena</t>
         </is>
       </c>
-      <c r="G68" s="4" t="n">
+      <c r="G68" s="7" t="n">
         <v>721</v>
       </c>
-      <c r="H68" s="4" t="n">
+      <c r="H68" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="I68" s="4" t="n">
+      <c r="I68" s="7" t="n">
         <v>2858</v>
       </c>
       <c r="J68" s="4" t="inlineStr">
@@ -3543,13 +3486,13 @@
           <t>Población Indígena</t>
         </is>
       </c>
-      <c r="G69" s="4" t="n">
+      <c r="G69" s="7" t="n">
         <v>84</v>
       </c>
-      <c r="H69" s="4" t="n">
+      <c r="H69" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="I69" s="4" t="n">
+      <c r="I69" s="7" t="n">
         <v>619</v>
       </c>
       <c r="J69" s="4" t="inlineStr">
@@ -3590,13 +3533,13 @@
           <t>Población Indígena</t>
         </is>
       </c>
-      <c r="G70" s="4" t="n">
+      <c r="G70" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="H70" s="4" t="n">
+      <c r="H70" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="I70" s="4" t="n">
+      <c r="I70" s="7" t="n">
         <v>138</v>
       </c>
       <c r="J70" s="4" t="inlineStr">
@@ -3637,13 +3580,13 @@
           <t>Discapacidad Auditiva</t>
         </is>
       </c>
-      <c r="G71" s="4" t="n">
+      <c r="G71" s="7" t="n">
         <v>1137</v>
       </c>
-      <c r="H71" s="4" t="n">
+      <c r="H71" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="I71" s="4" t="n">
+      <c r="I71" s="7" t="n">
         <v>7910</v>
       </c>
       <c r="J71" s="4" t="inlineStr">
@@ -3684,13 +3627,13 @@
           <t>Sheet1</t>
         </is>
       </c>
-      <c r="G72" s="4" t="n">
+      <c r="G72" s="7" t="n">
         <v>1144</v>
       </c>
-      <c r="H72" s="4" t="n">
+      <c r="H72" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="I72" s="4" t="n">
+      <c r="I72" s="7" t="n">
         <v>7916</v>
       </c>
       <c r="J72" s="4" t="inlineStr">
@@ -3731,13 +3674,13 @@
           <t>Sheet2</t>
         </is>
       </c>
-      <c r="G73" s="4" t="n">
+      <c r="G73" s="7" t="n">
         <v>1144</v>
       </c>
-      <c r="H73" s="4" t="n">
+      <c r="H73" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="I73" s="4" t="n">
+      <c r="I73" s="7" t="n">
         <v>7916</v>
       </c>
       <c r="J73" s="4" t="inlineStr">
@@ -3778,13 +3721,13 @@
           <t>Sheet3</t>
         </is>
       </c>
-      <c r="G74" s="4" t="n">
+      <c r="G74" s="7" t="n">
         <v>1144</v>
       </c>
-      <c r="H74" s="4" t="n">
+      <c r="H74" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="I74" s="4" t="n">
+      <c r="I74" s="7" t="n">
         <v>9045</v>
       </c>
       <c r="J74" s="4" t="inlineStr">
@@ -3825,13 +3768,13 @@
           <t>Servicios Básicos</t>
         </is>
       </c>
-      <c r="G75" s="4" t="n">
+      <c r="G75" s="7" t="n">
         <v>1136</v>
       </c>
-      <c r="H75" s="4" t="n">
+      <c r="H75" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="I75" s="4" t="n">
+      <c r="I75" s="7" t="n">
         <v>7909</v>
       </c>
       <c r="J75" s="4" t="inlineStr">
@@ -3872,13 +3815,13 @@
           <t>Condición de la Vivienda</t>
         </is>
       </c>
-      <c r="G76" s="4" t="n">
+      <c r="G76" s="7" t="n">
         <v>1272</v>
       </c>
-      <c r="H76" s="4" t="n">
+      <c r="H76" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="I76" s="4" t="n">
+      <c r="I76" s="7" t="n">
         <v>7910</v>
       </c>
       <c r="J76" s="4" t="inlineStr">
@@ -3919,13 +3862,13 @@
           <t>Deficiencia Económica</t>
         </is>
       </c>
-      <c r="G77" s="4" t="n">
+      <c r="G77" s="7" t="n">
         <v>1143</v>
       </c>
-      <c r="H77" s="4" t="n">
+      <c r="H77" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="I77" s="4" t="n">
+      <c r="I77" s="7" t="n">
         <v>7909</v>
       </c>
       <c r="J77" s="4" t="inlineStr">
@@ -3966,13 +3909,13 @@
           <t>Grupos de Edad</t>
         </is>
       </c>
-      <c r="G78" s="4" t="n">
+      <c r="G78" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="H78" s="4" t="n">
+      <c r="H78" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="I78" s="4" t="n">
+      <c r="I78" s="7" t="n">
         <v>623</v>
       </c>
       <c r="J78" s="4" t="inlineStr">
@@ -4013,13 +3956,13 @@
           <t>Población por Edad</t>
         </is>
       </c>
-      <c r="G79" s="4" t="n">
+      <c r="G79" s="7" t="n">
         <v>1186</v>
       </c>
-      <c r="H79" s="4" t="n">
+      <c r="H79" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="I79" s="4" t="n">
+      <c r="I79" s="7" t="n">
         <v>28249</v>
       </c>
       <c r="J79" s="4" t="inlineStr">
@@ -4060,13 +4003,13 @@
           <t>Hacinamiento</t>
         </is>
       </c>
-      <c r="G80" s="4" t="n">
+      <c r="G80" s="7" t="n">
         <v>1141</v>
       </c>
-      <c r="H80" s="4" t="n">
+      <c r="H80" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="I80" s="4" t="n">
+      <c r="I80" s="7" t="n">
         <v>7909</v>
       </c>
       <c r="J80" s="4" t="inlineStr">
@@ -4107,13 +4050,13 @@
           <t>Lugar de Nacimiento</t>
         </is>
       </c>
-      <c r="G81" s="4" t="n">
+      <c r="G81" s="7" t="n">
         <v>36</v>
       </c>
-      <c r="H81" s="4" t="n">
+      <c r="H81" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="I81" s="4" t="n">
+      <c r="I81" s="7" t="n">
         <v>165</v>
       </c>
       <c r="J81" s="4" t="inlineStr">
@@ -4154,13 +4097,13 @@
           <t>Lugar de Nacimiento</t>
         </is>
       </c>
-      <c r="G82" s="4" t="n">
+      <c r="G82" s="7" t="n">
         <v>1144</v>
       </c>
-      <c r="H82" s="4" t="n">
+      <c r="H82" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="I82" s="4" t="n">
+      <c r="I82" s="7" t="n">
         <v>9040</v>
       </c>
       <c r="J82" s="4" t="inlineStr">
@@ -4201,13 +4144,13 @@
           <t>Discapacidad Cardiovascular</t>
         </is>
       </c>
-      <c r="G83" s="4" t="n">
+      <c r="G83" s="7" t="n">
         <v>1148</v>
       </c>
-      <c r="H83" s="4" t="n">
+      <c r="H83" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="I83" s="4" t="n">
+      <c r="I83" s="7" t="n">
         <v>7910</v>
       </c>
       <c r="J83" s="4" t="inlineStr">
@@ -4248,13 +4191,13 @@
           <t>Discapacidad Mental-Intelectual</t>
         </is>
       </c>
-      <c r="G84" s="4" t="n">
+      <c r="G84" s="7" t="n">
         <v>1148</v>
       </c>
-      <c r="H84" s="4" t="n">
+      <c r="H84" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="I84" s="4" t="n">
+      <c r="I84" s="7" t="n">
         <v>7910</v>
       </c>
       <c r="J84" s="4" t="inlineStr">
@@ -4295,13 +4238,13 @@
           <t>Discapacidad Mental-Psicosocial</t>
         </is>
       </c>
-      <c r="G85" s="4" t="n">
+      <c r="G85" s="7" t="n">
         <v>1148</v>
       </c>
-      <c r="H85" s="4" t="n">
+      <c r="H85" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="I85" s="4" t="n">
+      <c r="I85" s="7" t="n">
         <v>7910</v>
       </c>
       <c r="J85" s="4" t="inlineStr">
@@ -4342,13 +4285,13 @@
           <t>Discapacida Musculo Esquelética</t>
         </is>
       </c>
-      <c r="G86" s="4" t="n">
+      <c r="G86" s="7" t="n">
         <v>1149</v>
       </c>
-      <c r="H86" s="4" t="n">
+      <c r="H86" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="I86" s="4" t="n">
+      <c r="I86" s="7" t="n">
         <v>7910</v>
       </c>
       <c r="J86" s="4" t="inlineStr">
@@ -4389,13 +4332,13 @@
           <t>Nacimiento en Vzla</t>
         </is>
       </c>
-      <c r="G87" s="4" t="n">
+      <c r="G87" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="H87" s="4" t="n">
+      <c r="H87" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="I87" s="4" t="n">
+      <c r="I87" s="7" t="n">
         <v>137</v>
       </c>
       <c r="J87" s="4" t="inlineStr">
@@ -4436,13 +4379,13 @@
           <t>Nacimiento en Venezuela</t>
         </is>
       </c>
-      <c r="G88" s="4" t="n">
+      <c r="G88" s="7" t="n">
         <v>1147</v>
       </c>
-      <c r="H88" s="4" t="n">
+      <c r="H88" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="I88" s="4" t="n">
+      <c r="I88" s="7" t="n">
         <v>7909</v>
       </c>
       <c r="J88" s="4" t="inlineStr">
@@ -4483,13 +4426,13 @@
           <t>Discapacidad Neurológica</t>
         </is>
       </c>
-      <c r="G89" s="4" t="n">
+      <c r="G89" s="7" t="n">
         <v>1148</v>
       </c>
-      <c r="H89" s="4" t="n">
+      <c r="H89" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="I89" s="4" t="n">
+      <c r="I89" s="7" t="n">
         <v>7910</v>
       </c>
       <c r="J89" s="4" t="inlineStr">
@@ -4530,13 +4473,13 @@
           <t>Población por Sexo</t>
         </is>
       </c>
-      <c r="G90" s="4" t="n">
+      <c r="G90" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="H90" s="4" t="n">
+      <c r="H90" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="I90" s="4" t="n">
+      <c r="I90" s="7" t="n">
         <v>137</v>
       </c>
       <c r="J90" s="4" t="inlineStr">
@@ -4577,13 +4520,13 @@
           <t>Población por Sexo</t>
         </is>
       </c>
-      <c r="G91" s="4" t="n">
+      <c r="G91" s="7" t="n">
         <v>1137</v>
       </c>
-      <c r="H91" s="4" t="n">
+      <c r="H91" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="I91" s="4" t="n">
+      <c r="I91" s="7" t="n">
         <v>7909</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
@@ -4624,13 +4567,13 @@
           <t>Discapacidad Respiratoria</t>
         </is>
       </c>
-      <c r="G92" s="4" t="n">
+      <c r="G92" s="7" t="n">
         <v>1148</v>
       </c>
-      <c r="H92" s="4" t="n">
+      <c r="H92" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="I92" s="4" t="n">
+      <c r="I92" s="7" t="n">
         <v>7910</v>
       </c>
       <c r="J92" s="4" t="inlineStr">
@@ -4671,13 +4614,13 @@
           <t>Discapacidad Visual</t>
         </is>
       </c>
-      <c r="G93" s="4" t="n">
+      <c r="G93" s="7" t="n">
         <v>1137</v>
       </c>
-      <c r="H93" s="4" t="n">
+      <c r="H93" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="I93" s="4" t="n">
+      <c r="I93" s="7" t="n">
         <v>7910</v>
       </c>
       <c r="J93" s="4" t="inlineStr">
@@ -4718,13 +4661,13 @@
           <t>Condición de Ocupación</t>
         </is>
       </c>
-      <c r="G94" s="4" t="n">
+      <c r="G94" s="7" t="n">
         <v>1138</v>
       </c>
-      <c r="H94" s="4" t="n">
+      <c r="H94" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="I94" s="4" t="n">
+      <c r="I94" s="7" t="n">
         <v>10169</v>
       </c>
       <c r="J94" s="4" t="inlineStr">
@@ -4765,13 +4708,13 @@
           <t>RESUMEN NACIONAL</t>
         </is>
       </c>
-      <c r="G95" s="4" t="n">
+      <c r="G95" s="7" t="n">
         <v>59</v>
       </c>
-      <c r="H95" s="4" t="n">
+      <c r="H95" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="I95" s="4" t="n">
+      <c r="I95" s="7" t="n">
         <v>119</v>
       </c>
       <c r="J95" s="4" t="inlineStr">
@@ -4812,13 +4755,13 @@
           <t>VIVIENDA ENTIDAD</t>
         </is>
       </c>
-      <c r="G96" s="4" t="n">
+      <c r="G96" s="7" t="n">
         <v>29</v>
       </c>
-      <c r="H96" s="4" t="n">
+      <c r="H96" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="I96" s="4" t="n">
+      <c r="I96" s="7" t="n">
         <v>271</v>
       </c>
       <c r="J96" s="4" t="inlineStr">
@@ -4859,13 +4802,13 @@
           <t>VIVIENDA MUNICIPIO</t>
         </is>
       </c>
-      <c r="G97" s="4" t="n">
+      <c r="G97" s="7" t="n">
         <v>340</v>
       </c>
-      <c r="H97" s="4" t="n">
+      <c r="H97" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="I97" s="4" t="n">
+      <c r="I97" s="7" t="n">
         <v>3382</v>
       </c>
       <c r="J97" s="4" t="inlineStr">
@@ -4906,13 +4849,13 @@
           <t>VIVIENDA PARROQUIA</t>
         </is>
       </c>
-      <c r="G98" s="4" t="n">
+      <c r="G98" s="7" t="n">
         <v>1132</v>
       </c>
-      <c r="H98" s="4" t="n">
+      <c r="H98" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="I98" s="4" t="n">
+      <c r="I98" s="7" t="n">
         <v>11302</v>
       </c>
       <c r="J98" s="4" t="inlineStr">
@@ -4953,13 +4896,13 @@
           <t>HOGARES ENTIDAD</t>
         </is>
       </c>
-      <c r="G99" s="4" t="n">
+      <c r="G99" s="7" t="n">
         <v>31</v>
       </c>
-      <c r="H99" s="4" t="n">
+      <c r="H99" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="I99" s="4" t="n">
+      <c r="I99" s="7" t="n">
         <v>649</v>
       </c>
       <c r="J99" s="4" t="inlineStr">
@@ -5000,13 +4943,13 @@
           <t>HOGARES MUNICIPIO</t>
         </is>
       </c>
-      <c r="G100" s="4" t="n">
+      <c r="G100" s="7" t="n">
         <v>342</v>
       </c>
-      <c r="H100" s="4" t="n">
+      <c r="H100" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="I100" s="4" t="n">
+      <c r="I100" s="7" t="n">
         <v>8113</v>
       </c>
       <c r="J100" s="4" t="inlineStr">
@@ -5047,13 +4990,13 @@
           <t>HOGARES PARROQUIA</t>
         </is>
       </c>
-      <c r="G101" s="4" t="n">
+      <c r="G101" s="7" t="n">
         <v>1134</v>
       </c>
-      <c r="H101" s="4" t="n">
+      <c r="H101" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="I101" s="4" t="n">
+      <c r="I101" s="7" t="n">
         <v>27122</v>
       </c>
       <c r="J101" s="4" t="inlineStr">
@@ -5094,13 +5037,13 @@
           <t>PERSONAS ENTIDAD</t>
         </is>
       </c>
-      <c r="G102" s="4" t="n">
+      <c r="G102" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="H102" s="4" t="n">
+      <c r="H102" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="I102" s="4" t="n">
+      <c r="I102" s="7" t="n">
         <v>784</v>
       </c>
       <c r="J102" s="4" t="inlineStr">
@@ -5141,13 +5084,13 @@
           <t>PERSONAS MUNICIPIO</t>
         </is>
       </c>
-      <c r="G103" s="4" t="n">
+      <c r="G103" s="7" t="n">
         <v>341</v>
       </c>
-      <c r="H103" s="4" t="n">
+      <c r="H103" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="I103" s="4" t="n">
+      <c r="I103" s="7" t="n">
         <v>9803</v>
       </c>
       <c r="J103" s="4" t="inlineStr">
@@ -5188,13 +5131,13 @@
           <t>PERSONAS PARROQUIA</t>
         </is>
       </c>
-      <c r="G104" s="4" t="n">
+      <c r="G104" s="7" t="n">
         <v>1133</v>
       </c>
-      <c r="H104" s="4" t="n">
+      <c r="H104" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="I104" s="4" t="n">
+      <c r="I104" s="7" t="n">
         <v>32771</v>
       </c>
       <c r="J104" s="4" t="inlineStr">
@@ -5235,13 +5178,13 @@
           <t>Discapacidad Voz y Habla</t>
         </is>
       </c>
-      <c r="G105" s="4" t="n">
+      <c r="G105" s="7" t="n">
         <v>1148</v>
       </c>
-      <c r="H105" s="4" t="n">
+      <c r="H105" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="I105" s="4" t="n">
+      <c r="I105" s="7" t="n">
         <v>7910</v>
       </c>
       <c r="J105" s="4" t="inlineStr">
@@ -5282,13 +5225,13 @@
           <t>Exportaciones Capítulo</t>
         </is>
       </c>
-      <c r="G106" s="4" t="n">
+      <c r="G106" s="7" t="n">
         <v>107</v>
       </c>
-      <c r="H106" s="4" t="n">
+      <c r="H106" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="I106" s="4" t="n">
+      <c r="I106" s="7" t="n">
         <v>2132</v>
       </c>
       <c r="J106" s="4" t="inlineStr">
@@ -5329,13 +5272,13 @@
           <t>Importaciones Capítulo</t>
         </is>
       </c>
-      <c r="G107" s="4" t="n">
+      <c r="G107" s="7" t="n">
         <v>107</v>
       </c>
-      <c r="H107" s="4" t="n">
+      <c r="H107" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="I107" s="4" t="n">
+      <c r="I107" s="7" t="n">
         <v>2182</v>
       </c>
       <c r="J107" s="4" t="inlineStr">
@@ -5376,13 +5319,13 @@
           <t>NACIONAL</t>
         </is>
       </c>
-      <c r="G108" s="4" t="n">
+      <c r="G108" s="7" t="n">
         <v>776</v>
       </c>
-      <c r="H108" s="4" t="n">
+      <c r="H108" s="7" t="n">
         <v>49</v>
       </c>
-      <c r="I108" s="4" t="n">
+      <c r="I108" s="7" t="n">
         <v>29868</v>
       </c>
       <c r="J108" s="4" t="inlineStr">
@@ -5423,13 +5366,13 @@
           <t>NBI</t>
         </is>
       </c>
-      <c r="G109" s="4" t="n">
+      <c r="G109" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="H109" s="4" t="n">
+      <c r="H109" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="I109" s="4" t="n">
+      <c r="I109" s="7" t="n">
         <v>300</v>
       </c>
       <c r="J109" s="4" t="inlineStr">
@@ -5470,13 +5413,13 @@
           <t>NBI</t>
         </is>
       </c>
-      <c r="G110" s="4" t="n">
+      <c r="G110" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="H110" s="4" t="n">
+      <c r="H110" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="I110" s="4" t="n">
+      <c r="I110" s="7" t="n">
         <v>165</v>
       </c>
       <c r="J110" s="4" t="inlineStr">
@@ -5517,13 +5460,13 @@
           <t>DIVORCIOS</t>
         </is>
       </c>
-      <c r="G111" s="4" t="n">
+      <c r="G111" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="H111" s="4" t="n">
+      <c r="H111" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="I111" s="4" t="n">
+      <c r="I111" s="7" t="n">
         <v>602</v>
       </c>
       <c r="J111" s="4" t="inlineStr">
@@ -5564,13 +5507,13 @@
           <t>DEFUNCIONES</t>
         </is>
       </c>
-      <c r="G112" s="4" t="n">
+      <c r="G112" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="H112" s="4" t="n">
+      <c r="H112" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="I112" s="4" t="n">
+      <c r="I112" s="7" t="n">
         <v>630</v>
       </c>
       <c r="J112" s="4" t="inlineStr">
@@ -5611,13 +5554,13 @@
           <t>MATRIMONIOS</t>
         </is>
       </c>
-      <c r="G113" s="4" t="n">
+      <c r="G113" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="H113" s="4" t="n">
+      <c r="H113" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="I113" s="4" t="n">
+      <c r="I113" s="7" t="n">
         <v>602</v>
       </c>
       <c r="J113" s="4" t="inlineStr">
@@ -5658,13 +5601,13 @@
           <t>NACIMIENTOS</t>
         </is>
       </c>
-      <c r="G114" s="4" t="n">
+      <c r="G114" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="H114" s="4" t="n">
+      <c r="H114" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="I114" s="4" t="n">
+      <c r="I114" s="7" t="n">
         <v>628</v>
       </c>
       <c r="J114" s="4" t="inlineStr">
@@ -5705,13 +5648,13 @@
           <t>DEFUNCIONES</t>
         </is>
       </c>
-      <c r="G115" s="4" t="n">
+      <c r="G115" s="7" t="n">
         <v>409</v>
       </c>
-      <c r="H115" s="4" t="n">
+      <c r="H115" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="I115" s="4" t="n">
+      <c r="I115" s="7" t="n">
         <v>2388</v>
       </c>
       <c r="J115" s="4" t="inlineStr">
@@ -5752,13 +5695,13 @@
           <t>MATRIMONIOS</t>
         </is>
       </c>
-      <c r="G116" s="4" t="n">
+      <c r="G116" s="7" t="n">
         <v>373</v>
       </c>
-      <c r="H116" s="4" t="n">
+      <c r="H116" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="I116" s="4" t="n">
+      <c r="I116" s="7" t="n">
         <v>2178</v>
       </c>
       <c r="J116" s="4" t="inlineStr">
@@ -5799,13 +5742,13 @@
           <t>NACIMIENTOS</t>
         </is>
       </c>
-      <c r="G117" s="4" t="n">
+      <c r="G117" s="7" t="n">
         <v>407</v>
       </c>
-      <c r="H117" s="4" t="n">
+      <c r="H117" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="I117" s="4" t="n">
+      <c r="I117" s="7" t="n">
         <v>2377</v>
       </c>
       <c r="J117" s="4" t="inlineStr">
@@ -5846,13 +5789,13 @@
           <t>SUICIDIOS</t>
         </is>
       </c>
-      <c r="G118" s="4" t="n">
+      <c r="G118" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="H118" s="4" t="n">
+      <c r="H118" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="I118" s="4" t="n">
+      <c r="I118" s="7" t="n">
         <v>603</v>
       </c>
       <c r="J118" s="4" t="inlineStr">
@@ -5893,13 +5836,13 @@
           <t>n_CEN</t>
         </is>
       </c>
-      <c r="G119" s="4" t="n">
+      <c r="G119" s="7" t="n">
         <v>666</v>
       </c>
-      <c r="H119" s="4" t="n">
+      <c r="H119" s="7" t="n">
         <v>77</v>
       </c>
-      <c r="I119" s="4" t="n">
+      <c r="I119" s="7" t="n">
         <v>50624</v>
       </c>
       <c r="J119" s="4" t="inlineStr">
@@ -5940,13 +5883,13 @@
           <t>Estado Amazonas</t>
         </is>
       </c>
-      <c r="G120" s="4" t="n">
+      <c r="G120" s="7" t="n">
         <v>36</v>
       </c>
-      <c r="H120" s="4" t="n">
+      <c r="H120" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="I120" s="4" t="n">
+      <c r="I120" s="7" t="n">
         <v>1303</v>
       </c>
       <c r="J120" s="4" t="inlineStr">
@@ -5987,13 +5930,13 @@
           <t>Estado Amazonas</t>
         </is>
       </c>
-      <c r="G121" s="4" t="n">
+      <c r="G121" s="7" t="n">
         <v>78</v>
       </c>
-      <c r="H121" s="4" t="n">
+      <c r="H121" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="I121" s="4" t="n">
+      <c r="I121" s="7" t="n">
         <v>807</v>
       </c>
       <c r="J121" s="4" t="inlineStr">
@@ -6034,13 +5977,13 @@
           <t>Estado Amazonas</t>
         </is>
       </c>
-      <c r="G122" s="4" t="n">
+      <c r="G122" s="7" t="n">
         <v>36</v>
       </c>
-      <c r="H122" s="4" t="n">
+      <c r="H122" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="I122" s="4" t="n">
+      <c r="I122" s="7" t="n">
         <v>1303</v>
       </c>
       <c r="J122" s="4" t="inlineStr">
@@ -6081,13 +6024,13 @@
           <t>n_CEN</t>
         </is>
       </c>
-      <c r="G123" s="4" t="n">
+      <c r="G123" s="7" t="n">
         <v>1384</v>
       </c>
-      <c r="H123" s="4" t="n">
+      <c r="H123" s="7" t="n">
         <v>77</v>
       </c>
-      <c r="I123" s="4" t="n">
+      <c r="I123" s="7" t="n">
         <v>105211</v>
       </c>
       <c r="J123" s="4" t="inlineStr">
@@ -6128,13 +6071,13 @@
           <t>Estado Anzoátegui</t>
         </is>
       </c>
-      <c r="G124" s="4" t="n">
+      <c r="G124" s="7" t="n">
         <v>78</v>
       </c>
-      <c r="H124" s="4" t="n">
+      <c r="H124" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="I124" s="4" t="n">
+      <c r="I124" s="7" t="n">
         <v>3487</v>
       </c>
       <c r="J124" s="4" t="inlineStr">
@@ -6175,13 +6118,13 @@
           <t>Estado Anzoátegui</t>
         </is>
       </c>
-      <c r="G125" s="4" t="n">
+      <c r="G125" s="7" t="n">
         <v>78</v>
       </c>
-      <c r="H125" s="4" t="n">
+      <c r="H125" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="I125" s="4" t="n">
+      <c r="I125" s="7" t="n">
         <v>807</v>
       </c>
       <c r="J125" s="4" t="inlineStr">
@@ -6222,13 +6165,13 @@
           <t>Estado Anzoátegui</t>
         </is>
       </c>
-      <c r="G126" s="4" t="n">
+      <c r="G126" s="7" t="n">
         <v>78</v>
       </c>
-      <c r="H126" s="4" t="n">
+      <c r="H126" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="I126" s="4" t="n">
+      <c r="I126" s="7" t="n">
         <v>3487</v>
       </c>
       <c r="J126" s="4" t="inlineStr">
@@ -6269,13 +6212,13 @@
           <t>n_CEN</t>
         </is>
       </c>
-      <c r="G127" s="4" t="n">
+      <c r="G127" s="7" t="n">
         <v>1392</v>
       </c>
-      <c r="H127" s="4" t="n">
+      <c r="H127" s="7" t="n">
         <v>77</v>
       </c>
-      <c r="I127" s="4" t="n">
+      <c r="I127" s="7" t="n">
         <v>105839</v>
       </c>
       <c r="J127" s="4" t="inlineStr">
@@ -6316,13 +6259,13 @@
           <t>Estado Apure</t>
         </is>
       </c>
-      <c r="G128" s="4" t="n">
+      <c r="G128" s="7" t="n">
         <v>36</v>
       </c>
-      <c r="H128" s="4" t="n">
+      <c r="H128" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="I128" s="4" t="n">
+      <c r="I128" s="7" t="n">
         <v>1303</v>
       </c>
       <c r="J128" s="4" t="inlineStr">
@@ -6363,13 +6306,13 @@
           <t>Estado Apure</t>
         </is>
       </c>
-      <c r="G129" s="4" t="n">
+      <c r="G129" s="7" t="n">
         <v>78</v>
       </c>
-      <c r="H129" s="4" t="n">
+      <c r="H129" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="I129" s="4" t="n">
+      <c r="I129" s="7" t="n">
         <v>807</v>
       </c>
       <c r="J129" s="4" t="inlineStr">
@@ -6410,13 +6353,13 @@
           <t>Estado Apure</t>
         </is>
       </c>
-      <c r="G130" s="4" t="n">
+      <c r="G130" s="7" t="n">
         <v>36</v>
       </c>
-      <c r="H130" s="4" t="n">
+      <c r="H130" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="I130" s="4" t="n">
+      <c r="I130" s="7" t="n">
         <v>1303</v>
       </c>
       <c r="J130" s="4" t="inlineStr">
@@ -6457,13 +6400,13 @@
           <t>n_CEN</t>
         </is>
       </c>
-      <c r="G131" s="4" t="n">
+      <c r="G131" s="7" t="n">
         <v>2011</v>
       </c>
-      <c r="H131" s="4" t="n">
+      <c r="H131" s="7" t="n">
         <v>77</v>
       </c>
-      <c r="I131" s="4" t="n">
+      <c r="I131" s="7" t="n">
         <v>152836</v>
       </c>
       <c r="J131" s="4" t="inlineStr">
@@ -6504,13 +6447,13 @@
           <t>Estado Barinas</t>
         </is>
       </c>
-      <c r="G132" s="4" t="n">
+      <c r="G132" s="7" t="n">
         <v>51</v>
       </c>
-      <c r="H132" s="4" t="n">
+      <c r="H132" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="I132" s="4" t="n">
+      <c r="I132" s="7" t="n">
         <v>2083</v>
       </c>
       <c r="J132" s="4" t="inlineStr">
@@ -6551,13 +6494,13 @@
           <t>Estado Barinas</t>
         </is>
       </c>
-      <c r="G133" s="4" t="n">
+      <c r="G133" s="7" t="n">
         <v>78</v>
       </c>
-      <c r="H133" s="4" t="n">
+      <c r="H133" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="I133" s="4" t="n">
+      <c r="I133" s="7" t="n">
         <v>807</v>
       </c>
       <c r="J133" s="4" t="inlineStr">
@@ -6598,13 +6541,13 @@
           <t>Estado Barinas</t>
         </is>
       </c>
-      <c r="G134" s="4" t="n">
+      <c r="G134" s="7" t="n">
         <v>51</v>
       </c>
-      <c r="H134" s="4" t="n">
+      <c r="H134" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="I134" s="4" t="n">
+      <c r="I134" s="7" t="n">
         <v>2083</v>
       </c>
       <c r="J134" s="4" t="inlineStr">
@@ -6645,13 +6588,13 @@
           <t>n_CEN</t>
         </is>
       </c>
-      <c r="G135" s="4" t="n">
+      <c r="G135" s="7" t="n">
         <v>1810</v>
       </c>
-      <c r="H135" s="4" t="n">
+      <c r="H135" s="7" t="n">
         <v>77</v>
       </c>
-      <c r="I135" s="4" t="n">
+      <c r="I135" s="7" t="n">
         <v>137582</v>
       </c>
       <c r="J135" s="4" t="inlineStr">
@@ -6692,13 +6635,13 @@
           <t>Estado Bolívar</t>
         </is>
       </c>
-      <c r="G136" s="4" t="n">
+      <c r="G136" s="7" t="n">
         <v>48</v>
       </c>
-      <c r="H136" s="4" t="n">
+      <c r="H136" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="I136" s="4" t="n">
+      <c r="I136" s="7" t="n">
         <v>1927</v>
       </c>
       <c r="J136" s="4" t="inlineStr">
@@ -6739,13 +6682,13 @@
           <t>Estado Bolívar</t>
         </is>
       </c>
-      <c r="G137" s="4" t="n">
+      <c r="G137" s="7" t="n">
         <v>78</v>
       </c>
-      <c r="H137" s="4" t="n">
+      <c r="H137" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="I137" s="4" t="n">
+      <c r="I137" s="7" t="n">
         <v>807</v>
       </c>
       <c r="J137" s="4" t="inlineStr">
@@ -6786,13 +6729,13 @@
           <t>Estado Bolívar</t>
         </is>
       </c>
-      <c r="G138" s="4" t="n">
+      <c r="G138" s="7" t="n">
         <v>48</v>
       </c>
-      <c r="H138" s="4" t="n">
+      <c r="H138" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="I138" s="4" t="n">
+      <c r="I138" s="7" t="n">
         <v>1927</v>
       </c>
       <c r="J138" s="4" t="inlineStr">
@@ -6833,13 +6776,13 @@
           <t>n_CEN</t>
         </is>
       </c>
-      <c r="G139" s="4" t="n">
+      <c r="G139" s="7" t="n">
         <v>388</v>
       </c>
-      <c r="H139" s="4" t="n">
+      <c r="H139" s="7" t="n">
         <v>77</v>
       </c>
-      <c r="I139" s="4" t="n">
+      <c r="I139" s="7" t="n">
         <v>29489</v>
       </c>
       <c r="J139" s="4" t="inlineStr">
@@ -6880,13 +6823,13 @@
           <t>Estado Carabobo</t>
         </is>
       </c>
-      <c r="G140" s="4" t="n">
+      <c r="G140" s="7" t="n">
         <v>57</v>
       </c>
-      <c r="H140" s="4" t="n">
+      <c r="H140" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="I140" s="4" t="n">
+      <c r="I140" s="7" t="n">
         <v>2395</v>
       </c>
       <c r="J140" s="4" t="inlineStr">
@@ -6927,13 +6870,13 @@
           <t>Estado Carabobo</t>
         </is>
       </c>
-      <c r="G141" s="4" t="n">
+      <c r="G141" s="7" t="n">
         <v>78</v>
       </c>
-      <c r="H141" s="4" t="n">
+      <c r="H141" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="I141" s="4" t="n">
+      <c r="I141" s="7" t="n">
         <v>807</v>
       </c>
       <c r="J141" s="4" t="inlineStr">
@@ -6974,13 +6917,13 @@
           <t>Estado Carabobo</t>
         </is>
       </c>
-      <c r="G142" s="4" t="n">
+      <c r="G142" s="7" t="n">
         <v>57</v>
       </c>
-      <c r="H142" s="4" t="n">
+      <c r="H142" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="I142" s="4" t="n">
+      <c r="I142" s="7" t="n">
         <v>2395</v>
       </c>
       <c r="J142" s="4" t="inlineStr">
@@ -7021,13 +6964,13 @@
           <t>n_CEN</t>
         </is>
       </c>
-      <c r="G143" s="4" t="n">
+      <c r="G143" s="7" t="n">
         <v>537</v>
       </c>
-      <c r="H143" s="4" t="n">
+      <c r="H143" s="7" t="n">
         <v>77</v>
       </c>
-      <c r="I143" s="4" t="n">
+      <c r="I143" s="7" t="n">
         <v>40813</v>
       </c>
       <c r="J143" s="4" t="inlineStr">
@@ -7068,13 +7011,13 @@
           <t>Estado Cojedes</t>
         </is>
       </c>
-      <c r="G144" s="4" t="n">
+      <c r="G144" s="7" t="n">
         <v>42</v>
       </c>
-      <c r="H144" s="4" t="n">
+      <c r="H144" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="I144" s="4" t="n">
+      <c r="I144" s="7" t="n">
         <v>1615</v>
       </c>
       <c r="J144" s="4" t="inlineStr">
@@ -7115,13 +7058,13 @@
           <t>Estado Cojedes</t>
         </is>
       </c>
-      <c r="G145" s="4" t="n">
+      <c r="G145" s="7" t="n">
         <v>78</v>
       </c>
-      <c r="H145" s="4" t="n">
+      <c r="H145" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="I145" s="4" t="n">
+      <c r="I145" s="7" t="n">
         <v>807</v>
       </c>
       <c r="J145" s="4" t="inlineStr">
@@ -7162,13 +7105,13 @@
           <t>Estado Cojedes</t>
         </is>
       </c>
-      <c r="G146" s="4" t="n">
+      <c r="G146" s="7" t="n">
         <v>42</v>
       </c>
-      <c r="H146" s="4" t="n">
+      <c r="H146" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="I146" s="4" t="n">
+      <c r="I146" s="7" t="n">
         <v>1615</v>
       </c>
       <c r="J146" s="4" t="inlineStr">
@@ -7209,13 +7152,13 @@
           <t>n_CEN</t>
         </is>
       </c>
-      <c r="G147" s="4" t="n">
+      <c r="G147" s="7" t="n">
         <v>587</v>
       </c>
-      <c r="H147" s="4" t="n">
+      <c r="H147" s="7" t="n">
         <v>77</v>
       </c>
-      <c r="I147" s="4" t="n">
+      <c r="I147" s="7" t="n">
         <v>44626</v>
       </c>
       <c r="J147" s="4" t="inlineStr">
@@ -7256,13 +7199,13 @@
           <t>Estado Delta Amacuro</t>
         </is>
       </c>
-      <c r="G148" s="4" t="n">
+      <c r="G148" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="H148" s="4" t="n">
+      <c r="H148" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="I148" s="4" t="n">
+      <c r="I148" s="7" t="n">
         <v>835</v>
       </c>
       <c r="J148" s="4" t="inlineStr">
@@ -7303,13 +7246,13 @@
           <t>Estado Delta Amacuro</t>
         </is>
       </c>
-      <c r="G149" s="4" t="n">
+      <c r="G149" s="7" t="n">
         <v>78</v>
       </c>
-      <c r="H149" s="4" t="n">
+      <c r="H149" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="I149" s="4" t="n">
+      <c r="I149" s="7" t="n">
         <v>807</v>
       </c>
       <c r="J149" s="4" t="inlineStr">
@@ -7350,13 +7293,13 @@
           <t>Estado Delta Amacuro</t>
         </is>
       </c>
-      <c r="G150" s="4" t="n">
+      <c r="G150" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="H150" s="4" t="n">
+      <c r="H150" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="I150" s="4" t="n">
+      <c r="I150" s="7" t="n">
         <v>835</v>
       </c>
       <c r="J150" s="4" t="inlineStr">
@@ -7397,13 +7340,13 @@
           <t>Dependencias Federales</t>
         </is>
       </c>
-      <c r="G151" s="4" t="n">
+      <c r="G151" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="H151" s="4" t="n">
+      <c r="H151" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="I151" s="4" t="n">
+      <c r="I151" s="7" t="n">
         <v>211</v>
       </c>
       <c r="J151" s="4" t="inlineStr">
@@ -7444,13 +7387,13 @@
           <t>Dependencias Federales</t>
         </is>
       </c>
-      <c r="G152" s="4" t="n">
+      <c r="G152" s="7" t="n">
         <v>78</v>
       </c>
-      <c r="H152" s="4" t="n">
+      <c r="H152" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="I152" s="4" t="n">
+      <c r="I152" s="7" t="n">
         <v>807</v>
       </c>
       <c r="J152" s="4" t="inlineStr">
@@ -7491,13 +7434,13 @@
           <t>Dependencias Federales</t>
         </is>
       </c>
-      <c r="G153" s="4" t="n">
+      <c r="G153" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="H153" s="4" t="n">
+      <c r="H153" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="I153" s="4" t="n">
+      <c r="I153" s="7" t="n">
         <v>211</v>
       </c>
       <c r="J153" s="4" t="inlineStr">
@@ -7538,13 +7481,13 @@
           <t>Distrito Capital</t>
         </is>
       </c>
-      <c r="G154" s="4" t="n">
+      <c r="G154" s="7" t="n">
         <v>81</v>
       </c>
-      <c r="H154" s="4" t="n">
+      <c r="H154" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="I154" s="4" t="n">
+      <c r="I154" s="7" t="n">
         <v>3643</v>
       </c>
       <c r="J154" s="4" t="inlineStr">
@@ -7585,13 +7528,13 @@
           <t>n_CEN</t>
         </is>
       </c>
-      <c r="G155" s="4" t="n">
+      <c r="G155" s="7" t="n">
         <v>29</v>
       </c>
-      <c r="H155" s="4" t="n">
+      <c r="H155" s="7" t="n">
         <v>77</v>
       </c>
-      <c r="I155" s="4" t="n">
+      <c r="I155" s="7" t="n">
         <v>2205</v>
       </c>
       <c r="J155" s="4" t="inlineStr">
@@ -7632,13 +7575,13 @@
           <t>Distrito Capital</t>
         </is>
       </c>
-      <c r="G156" s="4" t="n">
+      <c r="G156" s="7" t="n">
         <v>78</v>
       </c>
-      <c r="H156" s="4" t="n">
+      <c r="H156" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="I156" s="4" t="n">
+      <c r="I156" s="7" t="n">
         <v>807</v>
       </c>
       <c r="J156" s="4" t="inlineStr">
@@ -7679,13 +7622,13 @@
           <t>Distrito Capital</t>
         </is>
       </c>
-      <c r="G157" s="4" t="n">
+      <c r="G157" s="7" t="n">
         <v>81</v>
       </c>
-      <c r="H157" s="4" t="n">
+      <c r="H157" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="I157" s="4" t="n">
+      <c r="I157" s="7" t="n">
         <v>3643</v>
       </c>
       <c r="J157" s="4" t="inlineStr">
@@ -7726,13 +7669,13 @@
           <t>Estado Falcón</t>
         </is>
       </c>
-      <c r="G158" s="4" t="n">
+      <c r="G158" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="H158" s="4" t="n">
+      <c r="H158" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="I158" s="4" t="n">
+      <c r="I158" s="7" t="n">
         <v>4111</v>
       </c>
       <c r="J158" s="4" t="inlineStr">
@@ -7773,13 +7716,13 @@
           <t>Estado Falcón</t>
         </is>
       </c>
-      <c r="G159" s="4" t="n">
+      <c r="G159" s="7" t="n">
         <v>78</v>
       </c>
-      <c r="H159" s="4" t="n">
+      <c r="H159" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="I159" s="4" t="n">
+      <c r="I159" s="7" t="n">
         <v>807</v>
       </c>
       <c r="J159" s="4" t="inlineStr">
@@ -7820,13 +7763,13 @@
           <t>Estado Falcón</t>
         </is>
       </c>
-      <c r="G160" s="4" t="n">
+      <c r="G160" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="H160" s="4" t="n">
+      <c r="H160" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="I160" s="4" t="n">
+      <c r="I160" s="7" t="n">
         <v>4111</v>
       </c>
       <c r="J160" s="4" t="inlineStr">
@@ -7867,13 +7810,13 @@
           <t>n_CEN</t>
         </is>
       </c>
-      <c r="G161" s="4" t="n">
+      <c r="G161" s="7" t="n">
         <v>2086</v>
       </c>
-      <c r="H161" s="4" t="n">
+      <c r="H161" s="7" t="n">
         <v>77</v>
       </c>
-      <c r="I161" s="4" t="n">
+      <c r="I161" s="7" t="n">
         <v>158537</v>
       </c>
       <c r="J161" s="4" t="inlineStr">
@@ -7914,13 +7857,13 @@
           <t>Estado Guárico</t>
         </is>
       </c>
-      <c r="G162" s="4" t="n">
+      <c r="G162" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="H162" s="4" t="n">
+      <c r="H162" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="I162" s="4" t="n">
+      <c r="I162" s="7" t="n">
         <v>2551</v>
       </c>
       <c r="J162" s="4" t="inlineStr">
@@ -7961,13 +7904,13 @@
           <t>Estado Guárico</t>
         </is>
       </c>
-      <c r="G163" s="4" t="n">
+      <c r="G163" s="7" t="n">
         <v>78</v>
       </c>
-      <c r="H163" s="4" t="n">
+      <c r="H163" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="I163" s="4" t="n">
+      <c r="I163" s="7" t="n">
         <v>807</v>
       </c>
       <c r="J163" s="4" t="inlineStr">
@@ -8008,13 +7951,13 @@
           <t>Estado Guárico</t>
         </is>
       </c>
-      <c r="G164" s="4" t="n">
+      <c r="G164" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="H164" s="4" t="n">
+      <c r="H164" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="I164" s="4" t="n">
+      <c r="I164" s="7" t="n">
         <v>2551</v>
       </c>
       <c r="J164" s="4" t="inlineStr">
@@ -8055,13 +7998,13 @@
           <t>n_CEN</t>
         </is>
       </c>
-      <c r="G165" s="4" t="n">
+      <c r="G165" s="7" t="n">
         <v>2450</v>
       </c>
-      <c r="H165" s="4" t="n">
+      <c r="H165" s="7" t="n">
         <v>77</v>
       </c>
-      <c r="I165" s="4" t="n">
+      <c r="I165" s="7" t="n">
         <v>186201</v>
       </c>
       <c r="J165" s="4" t="inlineStr">
@@ -8102,13 +8045,13 @@
           <t>Estado Vargas</t>
         </is>
       </c>
-      <c r="G166" s="4" t="n">
+      <c r="G166" s="7" t="n">
         <v>48</v>
       </c>
-      <c r="H166" s="4" t="n">
+      <c r="H166" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="I166" s="4" t="n">
+      <c r="I166" s="7" t="n">
         <v>1927</v>
       </c>
       <c r="J166" s="4" t="inlineStr">
@@ -8149,13 +8092,13 @@
           <t>Estado Vargas</t>
         </is>
       </c>
-      <c r="G167" s="4" t="n">
+      <c r="G167" s="7" t="n">
         <v>78</v>
       </c>
-      <c r="H167" s="4" t="n">
+      <c r="H167" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="I167" s="4" t="n">
+      <c r="I167" s="7" t="n">
         <v>807</v>
       </c>
       <c r="J167" s="4" t="inlineStr">
@@ -8196,13 +8139,13 @@
           <t>Estado Vargas</t>
         </is>
       </c>
-      <c r="G168" s="4" t="n">
+      <c r="G168" s="7" t="n">
         <v>48</v>
       </c>
-      <c r="H168" s="4" t="n">
+      <c r="H168" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="I168" s="4" t="n">
+      <c r="I168" s="7" t="n">
         <v>1927</v>
       </c>
       <c r="J168" s="4" t="inlineStr">
@@ -8243,13 +8186,13 @@
           <t>n_CEN</t>
         </is>
       </c>
-      <c r="G169" s="4" t="n">
+      <c r="G169" s="7" t="n">
         <v>164</v>
       </c>
-      <c r="H169" s="4" t="n">
+      <c r="H169" s="7" t="n">
         <v>77</v>
       </c>
-      <c r="I169" s="4" t="n">
+      <c r="I169" s="7" t="n">
         <v>12465</v>
       </c>
       <c r="J169" s="4" t="inlineStr">
@@ -8290,13 +8233,13 @@
           <t>Indice de Masculinidad ENT</t>
         </is>
       </c>
-      <c r="G170" s="4" t="n">
+      <c r="G170" s="7" t="n">
         <v>86</v>
       </c>
-      <c r="H170" s="4" t="n">
+      <c r="H170" s="7" t="n">
         <v>55</v>
       </c>
-      <c r="I170" s="4" t="n">
+      <c r="I170" s="7" t="n">
         <v>4159</v>
       </c>
       <c r="J170" s="4" t="inlineStr">
@@ -8337,13 +8280,13 @@
           <t>Estado Lara</t>
         </is>
       </c>
-      <c r="G171" s="4" t="n">
+      <c r="G171" s="7" t="n">
         <v>42</v>
       </c>
-      <c r="H171" s="4" t="n">
+      <c r="H171" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="I171" s="4" t="n">
+      <c r="I171" s="7" t="n">
         <v>1615</v>
       </c>
       <c r="J171" s="4" t="inlineStr">
@@ -8384,13 +8327,13 @@
           <t>Estado Lara</t>
         </is>
       </c>
-      <c r="G172" s="4" t="n">
+      <c r="G172" s="7" t="n">
         <v>78</v>
       </c>
-      <c r="H172" s="4" t="n">
+      <c r="H172" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="I172" s="4" t="n">
+      <c r="I172" s="7" t="n">
         <v>807</v>
       </c>
       <c r="J172" s="4" t="inlineStr">
@@ -8431,13 +8374,13 @@
           <t>Indice de Masculinidad ENT</t>
         </is>
       </c>
-      <c r="G173" s="4" t="n">
+      <c r="G173" s="7" t="n">
         <v>86</v>
       </c>
-      <c r="H173" s="4" t="n">
+      <c r="H173" s="7" t="n">
         <v>55</v>
       </c>
-      <c r="I173" s="4" t="n">
+      <c r="I173" s="7" t="n">
         <v>4159</v>
       </c>
       <c r="J173" s="4" t="inlineStr">
@@ -8478,13 +8421,13 @@
           <t>Estado Lara</t>
         </is>
       </c>
-      <c r="G174" s="4" t="n">
+      <c r="G174" s="7" t="n">
         <v>42</v>
       </c>
-      <c r="H174" s="4" t="n">
+      <c r="H174" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="I174" s="4" t="n">
+      <c r="I174" s="7" t="n">
         <v>1615</v>
       </c>
       <c r="J174" s="4" t="inlineStr">
@@ -8525,13 +8468,13 @@
           <t>n_CEN</t>
         </is>
       </c>
-      <c r="G175" s="4" t="n">
+      <c r="G175" s="7" t="n">
         <v>2231</v>
       </c>
-      <c r="H175" s="4" t="n">
+      <c r="H175" s="7" t="n">
         <v>77</v>
       </c>
-      <c r="I175" s="4" t="n">
+      <c r="I175" s="7" t="n">
         <v>169557</v>
       </c>
       <c r="J175" s="4" t="inlineStr">
@@ -8572,13 +8515,13 @@
           <t>Estado Miranda</t>
         </is>
       </c>
-      <c r="G176" s="4" t="n">
+      <c r="G176" s="7" t="n">
         <v>78</v>
       </c>
-      <c r="H176" s="4" t="n">
+      <c r="H176" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="I176" s="4" t="n">
+      <c r="I176" s="7" t="n">
         <v>3487</v>
       </c>
       <c r="J176" s="4" t="inlineStr">
@@ -8619,13 +8562,13 @@
           <t>Estado Miranda</t>
         </is>
       </c>
-      <c r="G177" s="4" t="n">
+      <c r="G177" s="7" t="n">
         <v>78</v>
       </c>
-      <c r="H177" s="4" t="n">
+      <c r="H177" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="I177" s="4" t="n">
+      <c r="I177" s="7" t="n">
         <v>807</v>
       </c>
       <c r="J177" s="4" t="inlineStr">
@@ -8666,13 +8609,13 @@
           <t>Estado Miranda</t>
         </is>
       </c>
-      <c r="G178" s="4" t="n">
+      <c r="G178" s="7" t="n">
         <v>78</v>
       </c>
-      <c r="H178" s="4" t="n">
+      <c r="H178" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="I178" s="4" t="n">
+      <c r="I178" s="7" t="n">
         <v>3487</v>
       </c>
       <c r="J178" s="4" t="inlineStr">
@@ -8713,13 +8656,13 @@
           <t>n_CEN</t>
         </is>
       </c>
-      <c r="G179" s="4" t="n">
+      <c r="G179" s="7" t="n">
         <v>699</v>
       </c>
-      <c r="H179" s="4" t="n">
+      <c r="H179" s="7" t="n">
         <v>77</v>
       </c>
-      <c r="I179" s="4" t="n">
+      <c r="I179" s="7" t="n">
         <v>53125</v>
       </c>
       <c r="J179" s="4" t="inlineStr">
@@ -8760,13 +8703,13 @@
           <t>Estado Monagas</t>
         </is>
       </c>
-      <c r="G180" s="4" t="n">
+      <c r="G180" s="7" t="n">
         <v>54</v>
       </c>
-      <c r="H180" s="4" t="n">
+      <c r="H180" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="I180" s="4" t="n">
+      <c r="I180" s="7" t="n">
         <v>2239</v>
       </c>
       <c r="J180" s="4" t="inlineStr">
@@ -8807,13 +8750,13 @@
           <t>Estado Monagas</t>
         </is>
       </c>
-      <c r="G181" s="4" t="n">
+      <c r="G181" s="7" t="n">
         <v>78</v>
       </c>
-      <c r="H181" s="4" t="n">
+      <c r="H181" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="I181" s="4" t="n">
+      <c r="I181" s="7" t="n">
         <v>807</v>
       </c>
       <c r="J181" s="4" t="inlineStr">
@@ -8854,13 +8797,13 @@
           <t>Estado Monagas</t>
         </is>
       </c>
-      <c r="G182" s="4" t="n">
+      <c r="G182" s="7" t="n">
         <v>54</v>
       </c>
-      <c r="H182" s="4" t="n">
+      <c r="H182" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="I182" s="4" t="n">
+      <c r="I182" s="7" t="n">
         <v>2239</v>
       </c>
       <c r="J182" s="4" t="inlineStr">
@@ -8901,13 +8844,13 @@
           <t>n_CEN</t>
         </is>
       </c>
-      <c r="G183" s="4" t="n">
+      <c r="G183" s="7" t="n">
         <v>796</v>
       </c>
-      <c r="H183" s="4" t="n">
+      <c r="H183" s="7" t="n">
         <v>77</v>
       </c>
-      <c r="I183" s="4" t="n">
+      <c r="I183" s="7" t="n">
         <v>60507</v>
       </c>
       <c r="J183" s="4" t="inlineStr">
@@ -8948,13 +8891,13 @@
           <t>Estado Mérida</t>
         </is>
       </c>
-      <c r="G184" s="4" t="n">
+      <c r="G184" s="7" t="n">
         <v>84</v>
       </c>
-      <c r="H184" s="4" t="n">
+      <c r="H184" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="I184" s="4" t="n">
+      <c r="I184" s="7" t="n">
         <v>3799</v>
       </c>
       <c r="J184" s="4" t="inlineStr">
@@ -8995,13 +8938,13 @@
           <t>Estado Mérida</t>
         </is>
       </c>
-      <c r="G185" s="4" t="n">
+      <c r="G185" s="7" t="n">
         <v>78</v>
       </c>
-      <c r="H185" s="4" t="n">
+      <c r="H185" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="I185" s="4" t="n">
+      <c r="I185" s="7" t="n">
         <v>807</v>
       </c>
       <c r="J185" s="4" t="inlineStr">
@@ -9042,13 +8985,13 @@
           <t>Estado Mérida</t>
         </is>
       </c>
-      <c r="G186" s="4" t="n">
+      <c r="G186" s="7" t="n">
         <v>84</v>
       </c>
-      <c r="H186" s="4" t="n">
+      <c r="H186" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="I186" s="4" t="n">
+      <c r="I186" s="7" t="n">
         <v>3799</v>
       </c>
       <c r="J186" s="4" t="inlineStr">
@@ -9089,13 +9032,13 @@
           <t>n_CEN</t>
         </is>
       </c>
-      <c r="G187" s="4" t="n">
+      <c r="G187" s="7" t="n">
         <v>1649</v>
       </c>
-      <c r="H187" s="4" t="n">
+      <c r="H187" s="7" t="n">
         <v>77</v>
       </c>
-      <c r="I187" s="4" t="n">
+      <c r="I187" s="7" t="n">
         <v>125325</v>
       </c>
       <c r="J187" s="4" t="inlineStr">
@@ -9136,13 +9079,13 @@
           <t>Resumen Entidad</t>
         </is>
       </c>
-      <c r="G188" s="4" t="n">
+      <c r="G188" s="7" t="n">
         <v>93</v>
       </c>
-      <c r="H188" s="4" t="n">
+      <c r="H188" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="I188" s="4" t="n">
+      <c r="I188" s="7" t="n">
         <v>4113</v>
       </c>
       <c r="J188" s="4" t="inlineStr">
@@ -9183,13 +9126,13 @@
           <t>Nacional</t>
         </is>
       </c>
-      <c r="G189" s="4" t="n">
+      <c r="G189" s="7" t="n">
         <v>78</v>
       </c>
-      <c r="H189" s="4" t="n">
+      <c r="H189" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="I189" s="4" t="n">
+      <c r="I189" s="7" t="n">
         <v>807</v>
       </c>
       <c r="J189" s="4" t="inlineStr">
@@ -9230,13 +9173,13 @@
           <t>Indice de Masculinidad ENT</t>
         </is>
       </c>
-      <c r="G190" s="4" t="n">
+      <c r="G190" s="7" t="n">
         <v>86</v>
       </c>
-      <c r="H190" s="4" t="n">
+      <c r="H190" s="7" t="n">
         <v>55</v>
       </c>
-      <c r="I190" s="4" t="n">
+      <c r="I190" s="7" t="n">
         <v>4159</v>
       </c>
       <c r="J190" s="4" t="inlineStr">
@@ -9277,13 +9220,13 @@
           <t>Estado Nueva Esparta</t>
         </is>
       </c>
-      <c r="G191" s="4" t="n">
+      <c r="G191" s="7" t="n">
         <v>48</v>
       </c>
-      <c r="H191" s="4" t="n">
+      <c r="H191" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="I191" s="4" t="n">
+      <c r="I191" s="7" t="n">
         <v>1927</v>
       </c>
       <c r="J191" s="4" t="inlineStr">
@@ -9324,13 +9267,13 @@
           <t>Estado Nueva Esparta</t>
         </is>
       </c>
-      <c r="G192" s="4" t="n">
+      <c r="G192" s="7" t="n">
         <v>78</v>
       </c>
-      <c r="H192" s="4" t="n">
+      <c r="H192" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="I192" s="4" t="n">
+      <c r="I192" s="7" t="n">
         <v>807</v>
       </c>
       <c r="J192" s="4" t="inlineStr">
@@ -9371,13 +9314,13 @@
           <t>Indice de Masculinidad ENT</t>
         </is>
       </c>
-      <c r="G193" s="4" t="n">
+      <c r="G193" s="7" t="n">
         <v>86</v>
       </c>
-      <c r="H193" s="4" t="n">
+      <c r="H193" s="7" t="n">
         <v>55</v>
       </c>
-      <c r="I193" s="4" t="n">
+      <c r="I193" s="7" t="n">
         <v>4159</v>
       </c>
       <c r="J193" s="4" t="inlineStr">
@@ -9418,13 +9361,13 @@
           <t>Estado Nueva Esparta</t>
         </is>
       </c>
-      <c r="G194" s="4" t="n">
+      <c r="G194" s="7" t="n">
         <v>48</v>
       </c>
-      <c r="H194" s="4" t="n">
+      <c r="H194" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="I194" s="4" t="n">
+      <c r="I194" s="7" t="n">
         <v>1927</v>
       </c>
       <c r="J194" s="4" t="inlineStr">
@@ -9465,13 +9408,13 @@
           <t>n_CEN</t>
         </is>
       </c>
-      <c r="G195" s="4" t="n">
+      <c r="G195" s="7" t="n">
         <v>69</v>
       </c>
-      <c r="H195" s="4" t="n">
+      <c r="H195" s="7" t="n">
         <v>77</v>
       </c>
-      <c r="I195" s="4" t="n">
+      <c r="I195" s="7" t="n">
         <v>5245</v>
       </c>
       <c r="J195" s="4" t="inlineStr">
@@ -9512,13 +9455,13 @@
           <t>Estado Portuguesa</t>
         </is>
       </c>
-      <c r="G196" s="4" t="n">
+      <c r="G196" s="7" t="n">
         <v>57</v>
       </c>
-      <c r="H196" s="4" t="n">
+      <c r="H196" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="I196" s="4" t="n">
+      <c r="I196" s="7" t="n">
         <v>2395</v>
       </c>
       <c r="J196" s="4" t="inlineStr">
@@ -9559,13 +9502,13 @@
           <t>Estado Portuguesa</t>
         </is>
       </c>
-      <c r="G197" s="4" t="n">
+      <c r="G197" s="7" t="n">
         <v>78</v>
       </c>
-      <c r="H197" s="4" t="n">
+      <c r="H197" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="I197" s="4" t="n">
+      <c r="I197" s="7" t="n">
         <v>807</v>
       </c>
       <c r="J197" s="4" t="inlineStr">
@@ -9606,13 +9549,13 @@
           <t>Estado Portuguesa</t>
         </is>
       </c>
-      <c r="G198" s="4" t="n">
+      <c r="G198" s="7" t="n">
         <v>57</v>
       </c>
-      <c r="H198" s="4" t="n">
+      <c r="H198" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="I198" s="4" t="n">
+      <c r="I198" s="7" t="n">
         <v>2395</v>
       </c>
       <c r="J198" s="4" t="inlineStr">
@@ -9653,13 +9596,13 @@
           <t>n_CEN</t>
         </is>
       </c>
-      <c r="G199" s="4" t="n">
+      <c r="G199" s="7" t="n">
         <v>1600</v>
       </c>
-      <c r="H199" s="4" t="n">
+      <c r="H199" s="7" t="n">
         <v>77</v>
       </c>
-      <c r="I199" s="4" t="n">
+      <c r="I199" s="7" t="n">
         <v>121601</v>
       </c>
       <c r="J199" s="4" t="inlineStr">
@@ -9700,13 +9643,13 @@
           <t>Estado Sucre</t>
         </is>
       </c>
-      <c r="G200" s="4" t="n">
+      <c r="G200" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="H200" s="4" t="n">
+      <c r="H200" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="I200" s="4" t="n">
+      <c r="I200" s="7" t="n">
         <v>2551</v>
       </c>
       <c r="J200" s="4" t="inlineStr">
@@ -9747,13 +9690,13 @@
           <t>Estado Sucre</t>
         </is>
       </c>
-      <c r="G201" s="4" t="n">
+      <c r="G201" s="7" t="n">
         <v>78</v>
       </c>
-      <c r="H201" s="4" t="n">
+      <c r="H201" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="I201" s="4" t="n">
+      <c r="I201" s="7" t="n">
         <v>807</v>
       </c>
       <c r="J201" s="4" t="inlineStr">
@@ -9794,13 +9737,13 @@
           <t>Estado Sucre</t>
         </is>
       </c>
-      <c r="G202" s="4" t="n">
+      <c r="G202" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="H202" s="4" t="n">
+      <c r="H202" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="I202" s="4" t="n">
+      <c r="I202" s="7" t="n">
         <v>2551</v>
       </c>
       <c r="J202" s="4" t="inlineStr">
@@ -9841,13 +9784,13 @@
           <t>n_CEN</t>
         </is>
       </c>
-      <c r="G203" s="4" t="n">
+      <c r="G203" s="7" t="n">
         <v>874</v>
       </c>
-      <c r="H203" s="4" t="n">
+      <c r="H203" s="7" t="n">
         <v>77</v>
       </c>
-      <c r="I203" s="4" t="n">
+      <c r="I203" s="7" t="n">
         <v>66431</v>
       </c>
       <c r="J203" s="4" t="inlineStr">
@@ -9888,13 +9831,13 @@
           <t>Estado Táchira</t>
         </is>
       </c>
-      <c r="G204" s="4" t="n">
+      <c r="G204" s="7" t="n">
         <v>78</v>
       </c>
-      <c r="H204" s="4" t="n">
+      <c r="H204" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="I204" s="4" t="n">
+      <c r="I204" s="7" t="n">
         <v>807</v>
       </c>
       <c r="J204" s="4" t="inlineStr">
@@ -9935,13 +9878,13 @@
           <t>Estado Trujillo</t>
         </is>
       </c>
-      <c r="G205" s="4" t="n">
+      <c r="G205" s="7" t="n">
         <v>75</v>
       </c>
-      <c r="H205" s="4" t="n">
+      <c r="H205" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="I205" s="4" t="n">
+      <c r="I205" s="7" t="n">
         <v>3331</v>
       </c>
       <c r="J205" s="4" t="inlineStr">
@@ -9982,13 +9925,13 @@
           <t>Estado Trujillo</t>
         </is>
       </c>
-      <c r="G206" s="4" t="n">
+      <c r="G206" s="7" t="n">
         <v>78</v>
       </c>
-      <c r="H206" s="4" t="n">
+      <c r="H206" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="I206" s="4" t="n">
+      <c r="I206" s="7" t="n">
         <v>807</v>
       </c>
       <c r="J206" s="4" t="inlineStr">
@@ -10029,13 +9972,13 @@
           <t>Estado Trujillo</t>
         </is>
       </c>
-      <c r="G207" s="4" t="n">
+      <c r="G207" s="7" t="n">
         <v>75</v>
       </c>
-      <c r="H207" s="4" t="n">
+      <c r="H207" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="I207" s="4" t="n">
+      <c r="I207" s="7" t="n">
         <v>3331</v>
       </c>
       <c r="J207" s="4" t="inlineStr">
@@ -10076,13 +10019,13 @@
           <t>n_CEN</t>
         </is>
       </c>
-      <c r="G208" s="4" t="n">
+      <c r="G208" s="7" t="n">
         <v>1527</v>
       </c>
-      <c r="H208" s="4" t="n">
+      <c r="H208" s="7" t="n">
         <v>77</v>
       </c>
-      <c r="I208" s="4" t="n">
+      <c r="I208" s="7" t="n">
         <v>116054</v>
       </c>
       <c r="J208" s="4" t="inlineStr">
@@ -10123,13 +10066,13 @@
           <t>Estado Táchira</t>
         </is>
       </c>
-      <c r="G209" s="4" t="n">
+      <c r="G209" s="7" t="n">
         <v>102</v>
       </c>
-      <c r="H209" s="4" t="n">
+      <c r="H209" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="I209" s="4" t="n">
+      <c r="I209" s="7" t="n">
         <v>4735</v>
       </c>
       <c r="J209" s="4" t="inlineStr">
@@ -10170,13 +10113,13 @@
           <t>Estado Táchira</t>
         </is>
       </c>
-      <c r="G210" s="4" t="n">
+      <c r="G210" s="7" t="n">
         <v>102</v>
       </c>
-      <c r="H210" s="4" t="n">
+      <c r="H210" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="I210" s="4" t="n">
+      <c r="I210" s="7" t="n">
         <v>4735</v>
       </c>
       <c r="J210" s="4" t="inlineStr">
@@ -10217,13 +10160,13 @@
           <t>n_CEN</t>
         </is>
       </c>
-      <c r="G211" s="4" t="n">
+      <c r="G211" s="7" t="n">
         <v>1761</v>
       </c>
-      <c r="H211" s="4" t="n">
+      <c r="H211" s="7" t="n">
         <v>77</v>
       </c>
-      <c r="I211" s="4" t="n">
+      <c r="I211" s="7" t="n">
         <v>133843</v>
       </c>
       <c r="J211" s="4" t="inlineStr">
@@ -10264,13 +10207,13 @@
           <t>Estado Yaracuy</t>
         </is>
       </c>
-      <c r="G212" s="4" t="n">
+      <c r="G212" s="7" t="n">
         <v>57</v>
       </c>
-      <c r="H212" s="4" t="n">
+      <c r="H212" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="I212" s="4" t="n">
+      <c r="I212" s="7" t="n">
         <v>2395</v>
       </c>
       <c r="J212" s="4" t="inlineStr">
@@ -10311,13 +10254,13 @@
           <t>Estado Yaracuy</t>
         </is>
       </c>
-      <c r="G213" s="4" t="n">
+      <c r="G213" s="7" t="n">
         <v>78</v>
       </c>
-      <c r="H213" s="4" t="n">
+      <c r="H213" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="I213" s="4" t="n">
+      <c r="I213" s="7" t="n">
         <v>807</v>
       </c>
       <c r="J213" s="4" t="inlineStr">
@@ -10358,13 +10301,13 @@
           <t>Estado Yaracuy</t>
         </is>
       </c>
-      <c r="G214" s="4" t="n">
+      <c r="G214" s="7" t="n">
         <v>57</v>
       </c>
-      <c r="H214" s="4" t="n">
+      <c r="H214" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="I214" s="4" t="n">
+      <c r="I214" s="7" t="n">
         <v>2395</v>
       </c>
       <c r="J214" s="4" t="inlineStr">
@@ -10405,13 +10348,13 @@
           <t>n_CEN</t>
         </is>
       </c>
-      <c r="G215" s="4" t="n">
+      <c r="G215" s="7" t="n">
         <v>958</v>
       </c>
-      <c r="H215" s="4" t="n">
+      <c r="H215" s="7" t="n">
         <v>77</v>
       </c>
-      <c r="I215" s="4" t="n">
+      <c r="I215" s="7" t="n">
         <v>72810</v>
       </c>
       <c r="J215" s="4" t="inlineStr">
@@ -10452,13 +10395,13 @@
           <t>Estado Zulia</t>
         </is>
       </c>
-      <c r="G216" s="4" t="n">
+      <c r="G216" s="7" t="n">
         <v>78</v>
       </c>
-      <c r="H216" s="4" t="n">
+      <c r="H216" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="I216" s="4" t="n">
+      <c r="I216" s="7" t="n">
         <v>3487</v>
       </c>
       <c r="J216" s="4" t="inlineStr">
@@ -10499,13 +10442,13 @@
           <t>Estado Zulia</t>
         </is>
       </c>
-      <c r="G217" s="4" t="n">
+      <c r="G217" s="7" t="n">
         <v>78</v>
       </c>
-      <c r="H217" s="4" t="n">
+      <c r="H217" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="I217" s="4" t="n">
+      <c r="I217" s="7" t="n">
         <v>807</v>
       </c>
       <c r="J217" s="4" t="inlineStr">
@@ -10546,13 +10489,13 @@
           <t>Estado Zulia</t>
         </is>
       </c>
-      <c r="G218" s="4" t="n">
+      <c r="G218" s="7" t="n">
         <v>78</v>
       </c>
-      <c r="H218" s="4" t="n">
+      <c r="H218" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="I218" s="4" t="n">
+      <c r="I218" s="7" t="n">
         <v>3487</v>
       </c>
       <c r="J218" s="4" t="inlineStr">
@@ -10593,13 +10536,13 @@
           <t>n_CEN</t>
         </is>
       </c>
-      <c r="G219" s="4" t="n">
+      <c r="G219" s="7" t="n">
         <v>4825</v>
       </c>
-      <c r="H219" s="4" t="n">
+      <c r="H219" s="7" t="n">
         <v>77</v>
       </c>
-      <c r="I219" s="4" t="n">
+      <c r="I219" s="7" t="n">
         <v>366769</v>
       </c>
       <c r="J219" s="4" t="inlineStr">
@@ -10640,13 +10583,13 @@
           <t>Edad Simple</t>
         </is>
       </c>
-      <c r="G220" s="4" t="n">
+      <c r="G220" s="7" t="n">
         <v>318</v>
       </c>
-      <c r="H220" s="4" t="n">
+      <c r="H220" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="I220" s="4" t="n">
+      <c r="I220" s="7" t="n">
         <v>3687</v>
       </c>
       <c r="J220" s="4" t="inlineStr">
@@ -10687,13 +10630,13 @@
           <t>Esperanza de Vida</t>
         </is>
       </c>
-      <c r="G221" s="4" t="n">
+      <c r="G221" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="H221" s="4" t="n">
+      <c r="H221" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="I221" s="4" t="n">
+      <c r="I221" s="7" t="n">
         <v>217</v>
       </c>
       <c r="J221" s="4" t="inlineStr">
@@ -10734,13 +10677,13 @@
           <t>Resumen Entidad</t>
         </is>
       </c>
-      <c r="G222" s="4" t="n">
+      <c r="G222" s="7" t="n">
         <v>93</v>
       </c>
-      <c r="H222" s="4" t="n">
+      <c r="H222" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="I222" s="4" t="n">
+      <c r="I222" s="7" t="n">
         <v>4113</v>
       </c>
       <c r="J222" s="4" t="inlineStr">
@@ -10781,13 +10724,13 @@
           <t>n_CEN</t>
         </is>
       </c>
-      <c r="G223" s="4" t="n">
+      <c r="G223" s="7" t="n">
         <v>671</v>
       </c>
-      <c r="H223" s="4" t="n">
+      <c r="H223" s="7" t="n">
         <v>77</v>
       </c>
-      <c r="I223" s="4" t="n">
+      <c r="I223" s="7" t="n">
         <v>50997</v>
       </c>
       <c r="J223" s="4" t="inlineStr">
@@ -10828,13 +10771,13 @@
           <t>Estado Aragua</t>
         </is>
       </c>
-      <c r="G224" s="4" t="n">
+      <c r="G224" s="7" t="n">
         <v>69</v>
       </c>
-      <c r="H224" s="4" t="n">
+      <c r="H224" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="I224" s="4" t="n">
+      <c r="I224" s="7" t="n">
         <v>3019</v>
       </c>
       <c r="J224" s="4" t="inlineStr">
@@ -10875,13 +10818,13 @@
           <t>Estado Aragua</t>
         </is>
       </c>
-      <c r="G225" s="4" t="n">
+      <c r="G225" s="7" t="n">
         <v>78</v>
       </c>
-      <c r="H225" s="4" t="n">
+      <c r="H225" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="I225" s="4" t="n">
+      <c r="I225" s="7" t="n">
         <v>807</v>
       </c>
       <c r="J225" s="4" t="inlineStr">
@@ -10922,13 +10865,13 @@
           <t>Estado Aragua</t>
         </is>
       </c>
-      <c r="G226" s="4" t="n">
+      <c r="G226" s="7" t="n">
         <v>69</v>
       </c>
-      <c r="H226" s="4" t="n">
+      <c r="H226" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="I226" s="4" t="n">
+      <c r="I226" s="7" t="n">
         <v>3019</v>
       </c>
       <c r="J226" s="4" t="inlineStr">
@@ -11064,7 +11007,7 @@
           <t>Número de recursos</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B13" s="7" t="n">
         <v>323</v>
       </c>
     </row>
@@ -11074,7 +11017,7 @@
           <t>Recursos tabulares</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="7" t="n">
         <v>204</v>
       </c>
     </row>
@@ -11084,7 +11027,7 @@
           <t>Documentos</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n">
+      <c r="B15" s="7" t="n">
         <v>119</v>
       </c>
     </row>
@@ -11094,7 +11037,7 @@
           <t>Hojas extraídas</t>
         </is>
       </c>
-      <c r="B16" s="4" t="n">
+      <c r="B16" s="7" t="n">
         <v>220</v>
       </c>
     </row>
@@ -11104,7 +11047,7 @@
           <t>Celdas con valor extraídas</t>
         </is>
       </c>
-      <c r="B17" s="4" t="n">
+      <c r="B17" s="7" t="n">
         <v>2980320</v>
       </c>
     </row>

--- a/assets/data/ine/excel/ove_ine_venezuela_indice_hojas.xlsx
+++ b/assets/data/ine/excel/ove_ine_venezuela_indice_hojas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="indice_hojas" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metadatos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="indice_hojas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="metadatos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -81,23 +81,91 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -112,16 +180,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -130,7 +195,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -145,16 +210,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -572,13 +634,13 @@
           <t>Por Variables</t>
         </is>
       </c>
-      <c r="G7" s="7" t="n">
+      <c r="G7" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="H7" s="7" t="n">
+      <c r="H7" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="I7" s="7" t="n">
+      <c r="I7" s="5" t="n">
         <v>204</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -619,13 +681,13 @@
           <t>Pobres y Extremos</t>
         </is>
       </c>
-      <c r="G8" s="7" t="n">
+      <c r="G8" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="H8" s="7" t="n">
+      <c r="H8" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="I8" s="7" t="n">
+      <c r="I8" s="5" t="n">
         <v>186</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -666,13 +728,13 @@
           <t>Por Vriables</t>
         </is>
       </c>
-      <c r="G9" s="7" t="n">
+      <c r="G9" s="5" t="n">
         <v>63</v>
       </c>
-      <c r="H9" s="7" t="n">
+      <c r="H9" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="I9" s="7" t="n">
+      <c r="I9" s="5" t="n">
         <v>512</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -713,13 +775,13 @@
           <t>Pobres y Extremos</t>
         </is>
       </c>
-      <c r="G10" s="7" t="n">
+      <c r="G10" s="5" t="n">
         <v>63</v>
       </c>
-      <c r="H10" s="7" t="n">
+      <c r="H10" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="I10" s="7" t="n">
+      <c r="I10" s="5" t="n">
         <v>466</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -760,13 +822,13 @@
           <t>Por Variables</t>
         </is>
       </c>
-      <c r="G11" s="7" t="n">
+      <c r="G11" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="H11" s="7" t="n">
+      <c r="H11" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="I11" s="7" t="n">
+      <c r="I11" s="5" t="n">
         <v>204</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -807,13 +869,13 @@
           <t>Pobres y Extremos</t>
         </is>
       </c>
-      <c r="G12" s="7" t="n">
+      <c r="G12" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="H12" s="7" t="n">
+      <c r="H12" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="I12" s="7" t="n">
+      <c r="I12" s="5" t="n">
         <v>186</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -854,13 +916,13 @@
           <t>Por Variables</t>
         </is>
       </c>
-      <c r="G13" s="7" t="n">
+      <c r="G13" s="5" t="n">
         <v>57</v>
       </c>
-      <c r="H13" s="7" t="n">
+      <c r="H13" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="I13" s="7" t="n">
+      <c r="I13" s="5" t="n">
         <v>446</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -901,13 +963,13 @@
           <t>Pobres y Extremos</t>
         </is>
       </c>
-      <c r="G14" s="7" t="n">
+      <c r="G14" s="5" t="n">
         <v>45</v>
       </c>
-      <c r="H14" s="7" t="n">
+      <c r="H14" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="I14" s="7" t="n">
+      <c r="I14" s="5" t="n">
         <v>286</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -948,13 +1010,13 @@
           <t>Por Variables</t>
         </is>
       </c>
-      <c r="G15" s="7" t="n">
+      <c r="G15" s="5" t="n">
         <v>43</v>
       </c>
-      <c r="H15" s="7" t="n">
+      <c r="H15" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="I15" s="7" t="n">
+      <c r="I15" s="5" t="n">
         <v>292</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -995,13 +1057,13 @@
           <t>Pobres y Extremos</t>
         </is>
       </c>
-      <c r="G16" s="7" t="n">
+      <c r="G16" s="5" t="n">
         <v>43</v>
       </c>
-      <c r="H16" s="7" t="n">
+      <c r="H16" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="I16" s="7" t="n">
+      <c r="I16" s="5" t="n">
         <v>266</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1042,13 +1104,13 @@
           <t>Por Variables</t>
         </is>
       </c>
-      <c r="G17" s="7" t="n">
+      <c r="G17" s="5" t="n">
         <v>49</v>
       </c>
-      <c r="H17" s="7" t="n">
+      <c r="H17" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="I17" s="7" t="n">
+      <c r="I17" s="5" t="n">
         <v>358</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1089,13 +1151,13 @@
           <t>Pobres y Extremos</t>
         </is>
       </c>
-      <c r="G18" s="7" t="n">
+      <c r="G18" s="5" t="n">
         <v>49</v>
       </c>
-      <c r="H18" s="7" t="n">
+      <c r="H18" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="I18" s="7" t="n">
+      <c r="I18" s="5" t="n">
         <v>326</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1136,13 +1198,13 @@
           <t>Por Variables</t>
         </is>
       </c>
-      <c r="G19" s="7" t="n">
+      <c r="G19" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="H19" s="7" t="n">
+      <c r="H19" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="I19" s="7" t="n">
+      <c r="I19" s="5" t="n">
         <v>248</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1183,13 +1245,13 @@
           <t>Pobres y Extremos</t>
         </is>
       </c>
-      <c r="G20" s="7" t="n">
+      <c r="G20" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="H20" s="7" t="n">
+      <c r="H20" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="I20" s="7" t="n">
+      <c r="I20" s="5" t="n">
         <v>226</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1230,13 +1292,13 @@
           <t>Por Variables</t>
         </is>
       </c>
-      <c r="G21" s="7" t="n">
+      <c r="G21" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="H21" s="7" t="n">
+      <c r="H21" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="I21" s="7" t="n">
+      <c r="I21" s="5" t="n">
         <v>138</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -1277,13 +1339,13 @@
           <t>Pobres y Extremos</t>
         </is>
       </c>
-      <c r="G22" s="7" t="n">
+      <c r="G22" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="H22" s="7" t="n">
+      <c r="H22" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="I22" s="7" t="n">
+      <c r="I22" s="5" t="n">
         <v>126</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -1324,13 +1386,13 @@
           <t>Por Variables</t>
         </is>
       </c>
-      <c r="G23" s="7" t="n">
+      <c r="G23" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="H23" s="7" t="n">
+      <c r="H23" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="I23" s="7" t="n">
+      <c r="I23" s="5" t="n">
         <v>116</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -1371,13 +1433,13 @@
           <t>Pobres y Extremos</t>
         </is>
       </c>
-      <c r="G24" s="7" t="n">
+      <c r="G24" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="H24" s="7" t="n">
+      <c r="H24" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="I24" s="7" t="n">
+      <c r="I24" s="5" t="n">
         <v>106</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -1418,13 +1480,13 @@
           <t>Por Variables</t>
         </is>
       </c>
-      <c r="G25" s="7" t="n">
+      <c r="G25" s="5" t="n">
         <v>64</v>
       </c>
-      <c r="H25" s="7" t="n">
+      <c r="H25" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="I25" s="7" t="n">
+      <c r="I25" s="5" t="n">
         <v>534</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -1465,13 +1527,13 @@
           <t>POBREZA</t>
         </is>
       </c>
-      <c r="G26" s="7" t="n">
+      <c r="G26" s="5" t="n">
         <v>65</v>
       </c>
-      <c r="H26" s="7" t="n">
+      <c r="H26" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="I26" s="7" t="n">
+      <c r="I26" s="5" t="n">
         <v>486</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -1512,13 +1574,13 @@
           <t>Por Variables</t>
         </is>
       </c>
-      <c r="G27" s="7" t="n">
+      <c r="G27" s="5" t="n">
         <v>71</v>
       </c>
-      <c r="H27" s="7" t="n">
+      <c r="H27" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="I27" s="7" t="n">
+      <c r="I27" s="5" t="n">
         <v>600</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -1559,13 +1621,13 @@
           <t>Pobres y Extremos</t>
         </is>
       </c>
-      <c r="G28" s="7" t="n">
+      <c r="G28" s="5" t="n">
         <v>73</v>
       </c>
-      <c r="H28" s="7" t="n">
+      <c r="H28" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="I28" s="7" t="n">
+      <c r="I28" s="5" t="n">
         <v>546</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -1606,13 +1668,13 @@
           <t>Por Variables</t>
         </is>
       </c>
-      <c r="G29" s="7" t="n">
+      <c r="G29" s="5" t="n">
         <v>51</v>
       </c>
-      <c r="H29" s="7" t="n">
+      <c r="H29" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="I29" s="7" t="n">
+      <c r="I29" s="5" t="n">
         <v>380</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -1653,13 +1715,13 @@
           <t>Pobres y Extremos</t>
         </is>
       </c>
-      <c r="G30" s="7" t="n">
+      <c r="G30" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="H30" s="7" t="n">
+      <c r="H30" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="I30" s="7" t="n">
+      <c r="I30" s="5" t="n">
         <v>346</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -1700,13 +1762,13 @@
           <t>Por Variables</t>
         </is>
       </c>
-      <c r="G31" s="7" t="n">
+      <c r="G31" s="5" t="n">
         <v>44</v>
       </c>
-      <c r="H31" s="7" t="n">
+      <c r="H31" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="I31" s="7" t="n">
+      <c r="I31" s="5" t="n">
         <v>292</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -1747,13 +1809,13 @@
           <t>Pobres y Extremos</t>
         </is>
       </c>
-      <c r="G32" s="7" t="n">
+      <c r="G32" s="5" t="n">
         <v>44</v>
       </c>
-      <c r="H32" s="7" t="n">
+      <c r="H32" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="I32" s="7" t="n">
+      <c r="I32" s="5" t="n">
         <v>266</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -1794,13 +1856,13 @@
           <t>Por Variables</t>
         </is>
       </c>
-      <c r="G33" s="7" t="n">
+      <c r="G33" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="H33" s="7" t="n">
+      <c r="H33" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="I33" s="7" t="n">
+      <c r="I33" s="5" t="n">
         <v>248</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -1841,13 +1903,13 @@
           <t>Pobres y Extremos</t>
         </is>
       </c>
-      <c r="G34" s="7" t="n">
+      <c r="G34" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="H34" s="7" t="n">
+      <c r="H34" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="I34" s="7" t="n">
+      <c r="I34" s="5" t="n">
         <v>226</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -1888,13 +1950,13 @@
           <t xml:space="preserve">Por Variables </t>
         </is>
       </c>
-      <c r="G35" s="7" t="n">
+      <c r="G35" s="5" t="n">
         <v>63</v>
       </c>
-      <c r="H35" s="7" t="n">
+      <c r="H35" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="I35" s="7" t="n">
+      <c r="I35" s="5" t="n">
         <v>512</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -1935,13 +1997,13 @@
           <t>Pobres y Extremos</t>
         </is>
       </c>
-      <c r="G36" s="7" t="n">
+      <c r="G36" s="5" t="n">
         <v>63</v>
       </c>
-      <c r="H36" s="7" t="n">
+      <c r="H36" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="I36" s="7" t="n">
+      <c r="I36" s="5" t="n">
         <v>466</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
@@ -1982,13 +2044,13 @@
           <t>Por Variables</t>
         </is>
       </c>
-      <c r="G37" s="7" t="n">
+      <c r="G37" s="5" t="n">
         <v>47</v>
       </c>
-      <c r="H37" s="7" t="n">
+      <c r="H37" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="I37" s="7" t="n">
+      <c r="I37" s="5" t="n">
         <v>336</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -2029,13 +2091,13 @@
           <t>Pobres y Extremos</t>
         </is>
       </c>
-      <c r="G38" s="7" t="n">
+      <c r="G38" s="5" t="n">
         <v>47</v>
       </c>
-      <c r="H38" s="7" t="n">
+      <c r="H38" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="I38" s="7" t="n">
+      <c r="I38" s="5" t="n">
         <v>306</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
@@ -2076,13 +2138,13 @@
           <t>Por Variables</t>
         </is>
       </c>
-      <c r="G39" s="7" t="n">
+      <c r="G39" s="5" t="n">
         <v>67</v>
       </c>
-      <c r="H39" s="7" t="n">
+      <c r="H39" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="I39" s="7" t="n">
+      <c r="I39" s="5" t="n">
         <v>556</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -2123,13 +2185,13 @@
           <t>Pobres y Extremos</t>
         </is>
       </c>
-      <c r="G40" s="7" t="n">
+      <c r="G40" s="5" t="n">
         <v>66</v>
       </c>
-      <c r="H40" s="7" t="n">
+      <c r="H40" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="I40" s="7" t="n">
+      <c r="I40" s="5" t="n">
         <v>506</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
@@ -2170,13 +2232,13 @@
           <t>Variables</t>
         </is>
       </c>
-      <c r="G41" s="7" t="n">
+      <c r="G41" s="5" t="n">
         <v>77</v>
       </c>
-      <c r="H41" s="7" t="n">
+      <c r="H41" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="I41" s="7" t="n">
+      <c r="I41" s="5" t="n">
         <v>602</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
@@ -2217,13 +2279,13 @@
           <t>Pobres</t>
         </is>
       </c>
-      <c r="G42" s="7" t="n">
+      <c r="G42" s="5" t="n">
         <v>74</v>
       </c>
-      <c r="H42" s="7" t="n">
+      <c r="H42" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="I42" s="7" t="n">
+      <c r="I42" s="5" t="n">
         <v>548</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
@@ -2264,13 +2326,13 @@
           <t>Pobres y Extremos</t>
         </is>
       </c>
-      <c r="G43" s="7" t="n">
+      <c r="G43" s="5" t="n">
         <v>43</v>
       </c>
-      <c r="H43" s="7" t="n">
+      <c r="H43" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="I43" s="7" t="n">
+      <c r="I43" s="5" t="n">
         <v>266</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
@@ -2311,13 +2373,13 @@
           <t>Por Variables</t>
         </is>
       </c>
-      <c r="G44" s="7" t="n">
+      <c r="G44" s="5" t="n">
         <v>44</v>
       </c>
-      <c r="H44" s="7" t="n">
+      <c r="H44" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="I44" s="7" t="n">
+      <c r="I44" s="5" t="n">
         <v>292</v>
       </c>
       <c r="J44" s="4" t="inlineStr">
@@ -2358,13 +2420,13 @@
           <t>Pobres y Extremos</t>
         </is>
       </c>
-      <c r="G45" s="7" t="n">
+      <c r="G45" s="5" t="n">
         <v>49</v>
       </c>
-      <c r="H45" s="7" t="n">
+      <c r="H45" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="I45" s="7" t="n">
+      <c r="I45" s="5" t="n">
         <v>326</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
@@ -2405,13 +2467,13 @@
           <t>Por variables</t>
         </is>
       </c>
-      <c r="G46" s="7" t="n">
+      <c r="G46" s="5" t="n">
         <v>49</v>
       </c>
-      <c r="H46" s="7" t="n">
+      <c r="H46" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="I46" s="7" t="n">
+      <c r="I46" s="5" t="n">
         <v>358</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
@@ -2452,13 +2514,13 @@
           <t>Por Variables</t>
         </is>
       </c>
-      <c r="G47" s="7" t="n">
+      <c r="G47" s="5" t="n">
         <v>51</v>
       </c>
-      <c r="H47" s="7" t="n">
+      <c r="H47" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="I47" s="7" t="n">
+      <c r="I47" s="5" t="n">
         <v>380</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
@@ -2499,13 +2561,13 @@
           <t>Pobres y Extremos</t>
         </is>
       </c>
-      <c r="G48" s="7" t="n">
+      <c r="G48" s="5" t="n">
         <v>51</v>
       </c>
-      <c r="H48" s="7" t="n">
+      <c r="H48" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="I48" s="7" t="n">
+      <c r="I48" s="5" t="n">
         <v>346</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
@@ -2546,13 +2608,13 @@
           <t>Por Variables</t>
         </is>
       </c>
-      <c r="G49" s="7" t="n">
+      <c r="G49" s="5" t="n">
         <v>61</v>
       </c>
-      <c r="H49" s="7" t="n">
+      <c r="H49" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="I49" s="7" t="n">
+      <c r="I49" s="5" t="n">
         <v>490</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
@@ -2593,13 +2655,13 @@
           <t>Pobres y Extremos</t>
         </is>
       </c>
-      <c r="G50" s="7" t="n">
+      <c r="G50" s="5" t="n">
         <v>60</v>
       </c>
-      <c r="H50" s="7" t="n">
+      <c r="H50" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="I50" s="7" t="n">
+      <c r="I50" s="5" t="n">
         <v>446</v>
       </c>
       <c r="J50" s="4" t="inlineStr">
@@ -2640,13 +2702,13 @@
           <t>Por Variables</t>
         </is>
       </c>
-      <c r="G51" s="7" t="n">
+      <c r="G51" s="5" t="n">
         <v>78</v>
       </c>
-      <c r="H51" s="7" t="n">
+      <c r="H51" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="I51" s="7" t="n">
+      <c r="I51" s="5" t="n">
         <v>688</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
@@ -2687,13 +2749,13 @@
           <t>Pobres y Extremos</t>
         </is>
       </c>
-      <c r="G52" s="7" t="n">
+      <c r="G52" s="5" t="n">
         <v>79</v>
       </c>
-      <c r="H52" s="7" t="n">
+      <c r="H52" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="I52" s="7" t="n">
+      <c r="I52" s="5" t="n">
         <v>626</v>
       </c>
       <c r="J52" s="4" t="inlineStr">
@@ -2734,13 +2796,13 @@
           <t>Pobres y Extremos</t>
         </is>
       </c>
-      <c r="G53" s="7" t="n">
+      <c r="G53" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="H53" s="7" t="n">
+      <c r="H53" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="I53" s="7" t="n">
+      <c r="I53" s="5" t="n">
         <v>326</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
@@ -2781,13 +2843,13 @@
           <t>Por Variables</t>
         </is>
       </c>
-      <c r="G54" s="7" t="n">
+      <c r="G54" s="5" t="n">
         <v>49</v>
       </c>
-      <c r="H54" s="7" t="n">
+      <c r="H54" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="I54" s="7" t="n">
+      <c r="I54" s="5" t="n">
         <v>358</v>
       </c>
       <c r="J54" s="4" t="inlineStr">
@@ -2828,13 +2890,13 @@
           <t>Por Variables</t>
         </is>
       </c>
-      <c r="G55" s="7" t="n">
+      <c r="G55" s="5" t="n">
         <v>63</v>
       </c>
-      <c r="H55" s="7" t="n">
+      <c r="H55" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="I55" s="7" t="n">
+      <c r="I55" s="5" t="n">
         <v>512</v>
       </c>
       <c r="J55" s="4" t="inlineStr">
@@ -2875,13 +2937,13 @@
           <t>Pobres y Extremos</t>
         </is>
       </c>
-      <c r="G56" s="7" t="n">
+      <c r="G56" s="5" t="n">
         <v>63</v>
       </c>
-      <c r="H56" s="7" t="n">
+      <c r="H56" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="I56" s="7" t="n">
+      <c r="I56" s="5" t="n">
         <v>466</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
@@ -2922,13 +2984,13 @@
           <t>Servicio de Agua</t>
         </is>
       </c>
-      <c r="G57" s="7" t="n">
+      <c r="G57" s="5" t="n">
         <v>1137</v>
       </c>
-      <c r="H57" s="7" t="n">
+      <c r="H57" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="I57" s="7" t="n">
+      <c r="I57" s="5" t="n">
         <v>15820</v>
       </c>
       <c r="J57" s="4" t="inlineStr">
@@ -2969,13 +3031,13 @@
           <t>Población Indígena</t>
         </is>
       </c>
-      <c r="G58" s="7" t="n">
+      <c r="G58" s="5" t="n">
         <v>85</v>
       </c>
-      <c r="H58" s="7" t="n">
+      <c r="H58" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="I58" s="7" t="n">
+      <c r="I58" s="5" t="n">
         <v>387</v>
       </c>
       <c r="J58" s="4" t="inlineStr">
@@ -3016,13 +3078,13 @@
           <t>Servicio de Basura</t>
         </is>
       </c>
-      <c r="G59" s="7" t="n">
+      <c r="G59" s="5" t="n">
         <v>1137</v>
       </c>
-      <c r="H59" s="7" t="n">
+      <c r="H59" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="I59" s="7" t="n">
+      <c r="I59" s="5" t="n">
         <v>12430</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
@@ -3063,13 +3125,13 @@
           <t>Población Indígena</t>
         </is>
       </c>
-      <c r="G60" s="7" t="n">
+      <c r="G60" s="5" t="n">
         <v>160</v>
       </c>
-      <c r="H60" s="7" t="n">
+      <c r="H60" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="I60" s="7" t="n">
+      <c r="I60" s="5" t="n">
         <v>763</v>
       </c>
       <c r="J60" s="4" t="inlineStr">
@@ -3110,13 +3172,13 @@
           <t>Eliminación de Excretas</t>
         </is>
       </c>
-      <c r="G61" s="7" t="n">
+      <c r="G61" s="5" t="n">
         <v>1137</v>
       </c>
-      <c r="H61" s="7" t="n">
+      <c r="H61" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="I61" s="7" t="n">
+      <c r="I61" s="5" t="n">
         <v>11300</v>
       </c>
       <c r="J61" s="4" t="inlineStr">
@@ -3157,13 +3219,13 @@
           <t>Servicio Eléctrico</t>
         </is>
       </c>
-      <c r="G62" s="7" t="n">
+      <c r="G62" s="5" t="n">
         <v>1137</v>
       </c>
-      <c r="H62" s="7" t="n">
+      <c r="H62" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="I62" s="7" t="n">
+      <c r="I62" s="5" t="n">
         <v>12430</v>
       </c>
       <c r="J62" s="4" t="inlineStr">
@@ -3204,13 +3266,13 @@
           <t>Frecuencia Servicio Agua</t>
         </is>
       </c>
-      <c r="G63" s="7" t="n">
+      <c r="G63" s="5" t="n">
         <v>1137</v>
       </c>
-      <c r="H63" s="7" t="n">
+      <c r="H63" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="I63" s="7" t="n">
+      <c r="I63" s="5" t="n">
         <v>10170</v>
       </c>
       <c r="J63" s="4" t="inlineStr">
@@ -3251,13 +3313,13 @@
           <t>Frecuencia Servicio Basura</t>
         </is>
       </c>
-      <c r="G64" s="7" t="n">
+      <c r="G64" s="5" t="n">
         <v>1137</v>
       </c>
-      <c r="H64" s="7" t="n">
+      <c r="H64" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="I64" s="7" t="n">
+      <c r="I64" s="5" t="n">
         <v>10170</v>
       </c>
       <c r="J64" s="4" t="inlineStr">
@@ -3298,13 +3360,13 @@
           <t>Gas Directo</t>
         </is>
       </c>
-      <c r="G65" s="7" t="n">
+      <c r="G65" s="5" t="n">
         <v>1137</v>
       </c>
-      <c r="H65" s="7" t="n">
+      <c r="H65" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="I65" s="7" t="n">
+      <c r="I65" s="5" t="n">
         <v>7910</v>
       </c>
       <c r="J65" s="4" t="inlineStr">
@@ -3345,13 +3407,13 @@
           <t>Población Indígena</t>
         </is>
       </c>
-      <c r="G66" s="7" t="n">
+      <c r="G66" s="5" t="n">
         <v>535</v>
       </c>
-      <c r="H66" s="7" t="n">
+      <c r="H66" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="I66" s="7" t="n">
+      <c r="I66" s="5" t="n">
         <v>2637</v>
       </c>
       <c r="J66" s="4" t="inlineStr">
@@ -3392,13 +3454,13 @@
           <t>Población Indígena</t>
         </is>
       </c>
-      <c r="G67" s="7" t="n">
+      <c r="G67" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="H67" s="7" t="n">
+      <c r="H67" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="I67" s="7" t="n">
+      <c r="I67" s="5" t="n">
         <v>165</v>
       </c>
       <c r="J67" s="4" t="inlineStr">
@@ -3439,13 +3501,13 @@
           <t>Población Indígena</t>
         </is>
       </c>
-      <c r="G68" s="7" t="n">
+      <c r="G68" s="5" t="n">
         <v>721</v>
       </c>
-      <c r="H68" s="7" t="n">
+      <c r="H68" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="I68" s="7" t="n">
+      <c r="I68" s="5" t="n">
         <v>2858</v>
       </c>
       <c r="J68" s="4" t="inlineStr">
@@ -3486,13 +3548,13 @@
           <t>Población Indígena</t>
         </is>
       </c>
-      <c r="G69" s="7" t="n">
+      <c r="G69" s="5" t="n">
         <v>84</v>
       </c>
-      <c r="H69" s="7" t="n">
+      <c r="H69" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="I69" s="7" t="n">
+      <c r="I69" s="5" t="n">
         <v>619</v>
       </c>
       <c r="J69" s="4" t="inlineStr">
@@ -3533,13 +3595,13 @@
           <t>Población Indígena</t>
         </is>
       </c>
-      <c r="G70" s="7" t="n">
+      <c r="G70" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="H70" s="7" t="n">
+      <c r="H70" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="I70" s="7" t="n">
+      <c r="I70" s="5" t="n">
         <v>138</v>
       </c>
       <c r="J70" s="4" t="inlineStr">
@@ -3580,13 +3642,13 @@
           <t>Discapacidad Auditiva</t>
         </is>
       </c>
-      <c r="G71" s="7" t="n">
+      <c r="G71" s="5" t="n">
         <v>1137</v>
       </c>
-      <c r="H71" s="7" t="n">
+      <c r="H71" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="I71" s="7" t="n">
+      <c r="I71" s="5" t="n">
         <v>7910</v>
       </c>
       <c r="J71" s="4" t="inlineStr">
@@ -3627,13 +3689,13 @@
           <t>Sheet1</t>
         </is>
       </c>
-      <c r="G72" s="7" t="n">
+      <c r="G72" s="5" t="n">
         <v>1144</v>
       </c>
-      <c r="H72" s="7" t="n">
+      <c r="H72" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="I72" s="7" t="n">
+      <c r="I72" s="5" t="n">
         <v>7916</v>
       </c>
       <c r="J72" s="4" t="inlineStr">
@@ -3674,13 +3736,13 @@
           <t>Sheet2</t>
         </is>
       </c>
-      <c r="G73" s="7" t="n">
+      <c r="G73" s="5" t="n">
         <v>1144</v>
       </c>
-      <c r="H73" s="7" t="n">
+      <c r="H73" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="I73" s="7" t="n">
+      <c r="I73" s="5" t="n">
         <v>7916</v>
       </c>
       <c r="J73" s="4" t="inlineStr">
@@ -3721,13 +3783,13 @@
           <t>Sheet3</t>
         </is>
       </c>
-      <c r="G74" s="7" t="n">
+      <c r="G74" s="5" t="n">
         <v>1144</v>
       </c>
-      <c r="H74" s="7" t="n">
+      <c r="H74" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="I74" s="7" t="n">
+      <c r="I74" s="5" t="n">
         <v>9045</v>
       </c>
       <c r="J74" s="4" t="inlineStr">
@@ -3768,13 +3830,13 @@
           <t>Servicios Básicos</t>
         </is>
       </c>
-      <c r="G75" s="7" t="n">
+      <c r="G75" s="5" t="n">
         <v>1136</v>
       </c>
-      <c r="H75" s="7" t="n">
+      <c r="H75" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="I75" s="7" t="n">
+      <c r="I75" s="5" t="n">
         <v>7909</v>
       </c>
       <c r="J75" s="4" t="inlineStr">
@@ -3815,13 +3877,13 @@
           <t>Condición de la Vivienda</t>
         </is>
       </c>
-      <c r="G76" s="7" t="n">
+      <c r="G76" s="5" t="n">
         <v>1272</v>
       </c>
-      <c r="H76" s="7" t="n">
+      <c r="H76" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="I76" s="7" t="n">
+      <c r="I76" s="5" t="n">
         <v>7910</v>
       </c>
       <c r="J76" s="4" t="inlineStr">
@@ -3862,13 +3924,13 @@
           <t>Deficiencia Económica</t>
         </is>
       </c>
-      <c r="G77" s="7" t="n">
+      <c r="G77" s="5" t="n">
         <v>1143</v>
       </c>
-      <c r="H77" s="7" t="n">
+      <c r="H77" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="I77" s="7" t="n">
+      <c r="I77" s="5" t="n">
         <v>7909</v>
       </c>
       <c r="J77" s="4" t="inlineStr">
@@ -3909,13 +3971,13 @@
           <t>Grupos de Edad</t>
         </is>
       </c>
-      <c r="G78" s="7" t="n">
+      <c r="G78" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="H78" s="7" t="n">
+      <c r="H78" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="I78" s="7" t="n">
+      <c r="I78" s="5" t="n">
         <v>623</v>
       </c>
       <c r="J78" s="4" t="inlineStr">
@@ -3956,13 +4018,13 @@
           <t>Población por Edad</t>
         </is>
       </c>
-      <c r="G79" s="7" t="n">
+      <c r="G79" s="5" t="n">
         <v>1186</v>
       </c>
-      <c r="H79" s="7" t="n">
+      <c r="H79" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="I79" s="7" t="n">
+      <c r="I79" s="5" t="n">
         <v>28249</v>
       </c>
       <c r="J79" s="4" t="inlineStr">
@@ -4003,13 +4065,13 @@
           <t>Hacinamiento</t>
         </is>
       </c>
-      <c r="G80" s="7" t="n">
+      <c r="G80" s="5" t="n">
         <v>1141</v>
       </c>
-      <c r="H80" s="7" t="n">
+      <c r="H80" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="I80" s="7" t="n">
+      <c r="I80" s="5" t="n">
         <v>7909</v>
       </c>
       <c r="J80" s="4" t="inlineStr">
@@ -4050,13 +4112,13 @@
           <t>Lugar de Nacimiento</t>
         </is>
       </c>
-      <c r="G81" s="7" t="n">
+      <c r="G81" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="H81" s="7" t="n">
+      <c r="H81" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="I81" s="7" t="n">
+      <c r="I81" s="5" t="n">
         <v>165</v>
       </c>
       <c r="J81" s="4" t="inlineStr">
@@ -4097,13 +4159,13 @@
           <t>Lugar de Nacimiento</t>
         </is>
       </c>
-      <c r="G82" s="7" t="n">
+      <c r="G82" s="5" t="n">
         <v>1144</v>
       </c>
-      <c r="H82" s="7" t="n">
+      <c r="H82" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="I82" s="7" t="n">
+      <c r="I82" s="5" t="n">
         <v>9040</v>
       </c>
       <c r="J82" s="4" t="inlineStr">
@@ -4144,13 +4206,13 @@
           <t>Discapacidad Cardiovascular</t>
         </is>
       </c>
-      <c r="G83" s="7" t="n">
+      <c r="G83" s="5" t="n">
         <v>1148</v>
       </c>
-      <c r="H83" s="7" t="n">
+      <c r="H83" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="I83" s="7" t="n">
+      <c r="I83" s="5" t="n">
         <v>7910</v>
       </c>
       <c r="J83" s="4" t="inlineStr">
@@ -4191,13 +4253,13 @@
           <t>Discapacidad Mental-Intelectual</t>
         </is>
       </c>
-      <c r="G84" s="7" t="n">
+      <c r="G84" s="5" t="n">
         <v>1148</v>
       </c>
-      <c r="H84" s="7" t="n">
+      <c r="H84" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="I84" s="7" t="n">
+      <c r="I84" s="5" t="n">
         <v>7910</v>
       </c>
       <c r="J84" s="4" t="inlineStr">
@@ -4238,13 +4300,13 @@
           <t>Discapacidad Mental-Psicosocial</t>
         </is>
       </c>
-      <c r="G85" s="7" t="n">
+      <c r="G85" s="5" t="n">
         <v>1148</v>
       </c>
-      <c r="H85" s="7" t="n">
+      <c r="H85" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="I85" s="7" t="n">
+      <c r="I85" s="5" t="n">
         <v>7910</v>
       </c>
       <c r="J85" s="4" t="inlineStr">
@@ -4285,13 +4347,13 @@
           <t>Discapacida Musculo Esquelética</t>
         </is>
       </c>
-      <c r="G86" s="7" t="n">
+      <c r="G86" s="5" t="n">
         <v>1149</v>
       </c>
-      <c r="H86" s="7" t="n">
+      <c r="H86" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="I86" s="7" t="n">
+      <c r="I86" s="5" t="n">
         <v>7910</v>
       </c>
       <c r="J86" s="4" t="inlineStr">
@@ -4332,13 +4394,13 @@
           <t>Nacimiento en Vzla</t>
         </is>
       </c>
-      <c r="G87" s="7" t="n">
+      <c r="G87" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="H87" s="7" t="n">
+      <c r="H87" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="I87" s="7" t="n">
+      <c r="I87" s="5" t="n">
         <v>137</v>
       </c>
       <c r="J87" s="4" t="inlineStr">
@@ -4379,13 +4441,13 @@
           <t>Nacimiento en Venezuela</t>
         </is>
       </c>
-      <c r="G88" s="7" t="n">
+      <c r="G88" s="5" t="n">
         <v>1147</v>
       </c>
-      <c r="H88" s="7" t="n">
+      <c r="H88" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="I88" s="7" t="n">
+      <c r="I88" s="5" t="n">
         <v>7909</v>
       </c>
       <c r="J88" s="4" t="inlineStr">
@@ -4426,13 +4488,13 @@
           <t>Discapacidad Neurológica</t>
         </is>
       </c>
-      <c r="G89" s="7" t="n">
+      <c r="G89" s="5" t="n">
         <v>1148</v>
       </c>
-      <c r="H89" s="7" t="n">
+      <c r="H89" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="I89" s="7" t="n">
+      <c r="I89" s="5" t="n">
         <v>7910</v>
       </c>
       <c r="J89" s="4" t="inlineStr">
@@ -4473,13 +4535,13 @@
           <t>Población por Sexo</t>
         </is>
       </c>
-      <c r="G90" s="7" t="n">
+      <c r="G90" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="H90" s="7" t="n">
+      <c r="H90" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="I90" s="7" t="n">
+      <c r="I90" s="5" t="n">
         <v>137</v>
       </c>
       <c r="J90" s="4" t="inlineStr">
@@ -4520,13 +4582,13 @@
           <t>Población por Sexo</t>
         </is>
       </c>
-      <c r="G91" s="7" t="n">
+      <c r="G91" s="5" t="n">
         <v>1137</v>
       </c>
-      <c r="H91" s="7" t="n">
+      <c r="H91" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="I91" s="7" t="n">
+      <c r="I91" s="5" t="n">
         <v>7909</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
@@ -4567,13 +4629,13 @@
           <t>Discapacidad Respiratoria</t>
         </is>
       </c>
-      <c r="G92" s="7" t="n">
+      <c r="G92" s="5" t="n">
         <v>1148</v>
       </c>
-      <c r="H92" s="7" t="n">
+      <c r="H92" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="I92" s="7" t="n">
+      <c r="I92" s="5" t="n">
         <v>7910</v>
       </c>
       <c r="J92" s="4" t="inlineStr">
@@ -4614,13 +4676,13 @@
           <t>Discapacidad Visual</t>
         </is>
       </c>
-      <c r="G93" s="7" t="n">
+      <c r="G93" s="5" t="n">
         <v>1137</v>
       </c>
-      <c r="H93" s="7" t="n">
+      <c r="H93" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="I93" s="7" t="n">
+      <c r="I93" s="5" t="n">
         <v>7910</v>
       </c>
       <c r="J93" s="4" t="inlineStr">
@@ -4661,13 +4723,13 @@
           <t>Condición de Ocupación</t>
         </is>
       </c>
-      <c r="G94" s="7" t="n">
+      <c r="G94" s="5" t="n">
         <v>1138</v>
       </c>
-      <c r="H94" s="7" t="n">
+      <c r="H94" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="I94" s="7" t="n">
+      <c r="I94" s="5" t="n">
         <v>10169</v>
       </c>
       <c r="J94" s="4" t="inlineStr">
@@ -4708,13 +4770,13 @@
           <t>RESUMEN NACIONAL</t>
         </is>
       </c>
-      <c r="G95" s="7" t="n">
+      <c r="G95" s="5" t="n">
         <v>59</v>
       </c>
-      <c r="H95" s="7" t="n">
+      <c r="H95" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="I95" s="7" t="n">
+      <c r="I95" s="5" t="n">
         <v>119</v>
       </c>
       <c r="J95" s="4" t="inlineStr">
@@ -4755,13 +4817,13 @@
           <t>VIVIENDA ENTIDAD</t>
         </is>
       </c>
-      <c r="G96" s="7" t="n">
+      <c r="G96" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="H96" s="7" t="n">
+      <c r="H96" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="I96" s="7" t="n">
+      <c r="I96" s="5" t="n">
         <v>271</v>
       </c>
       <c r="J96" s="4" t="inlineStr">
@@ -4802,13 +4864,13 @@
           <t>VIVIENDA MUNICIPIO</t>
         </is>
       </c>
-      <c r="G97" s="7" t="n">
+      <c r="G97" s="5" t="n">
         <v>340</v>
       </c>
-      <c r="H97" s="7" t="n">
+      <c r="H97" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="I97" s="7" t="n">
+      <c r="I97" s="5" t="n">
         <v>3382</v>
       </c>
       <c r="J97" s="4" t="inlineStr">
@@ -4849,13 +4911,13 @@
           <t>VIVIENDA PARROQUIA</t>
         </is>
       </c>
-      <c r="G98" s="7" t="n">
+      <c r="G98" s="5" t="n">
         <v>1132</v>
       </c>
-      <c r="H98" s="7" t="n">
+      <c r="H98" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="I98" s="7" t="n">
+      <c r="I98" s="5" t="n">
         <v>11302</v>
       </c>
       <c r="J98" s="4" t="inlineStr">
@@ -4896,13 +4958,13 @@
           <t>HOGARES ENTIDAD</t>
         </is>
       </c>
-      <c r="G99" s="7" t="n">
+      <c r="G99" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="H99" s="7" t="n">
+      <c r="H99" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="I99" s="7" t="n">
+      <c r="I99" s="5" t="n">
         <v>649</v>
       </c>
       <c r="J99" s="4" t="inlineStr">
@@ -4943,13 +5005,13 @@
           <t>HOGARES MUNICIPIO</t>
         </is>
       </c>
-      <c r="G100" s="7" t="n">
+      <c r="G100" s="5" t="n">
         <v>342</v>
       </c>
-      <c r="H100" s="7" t="n">
+      <c r="H100" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="I100" s="7" t="n">
+      <c r="I100" s="5" t="n">
         <v>8113</v>
       </c>
       <c r="J100" s="4" t="inlineStr">
@@ -4990,13 +5052,13 @@
           <t>HOGARES PARROQUIA</t>
         </is>
       </c>
-      <c r="G101" s="7" t="n">
+      <c r="G101" s="5" t="n">
         <v>1134</v>
       </c>
-      <c r="H101" s="7" t="n">
+      <c r="H101" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="I101" s="7" t="n">
+      <c r="I101" s="5" t="n">
         <v>27122</v>
       </c>
       <c r="J101" s="4" t="inlineStr">
@@ -5037,13 +5099,13 @@
           <t>PERSONAS ENTIDAD</t>
         </is>
       </c>
-      <c r="G102" s="7" t="n">
+      <c r="G102" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="H102" s="7" t="n">
+      <c r="H102" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="I102" s="7" t="n">
+      <c r="I102" s="5" t="n">
         <v>784</v>
       </c>
       <c r="J102" s="4" t="inlineStr">
@@ -5084,13 +5146,13 @@
           <t>PERSONAS MUNICIPIO</t>
         </is>
       </c>
-      <c r="G103" s="7" t="n">
+      <c r="G103" s="5" t="n">
         <v>341</v>
       </c>
-      <c r="H103" s="7" t="n">
+      <c r="H103" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="I103" s="7" t="n">
+      <c r="I103" s="5" t="n">
         <v>9803</v>
       </c>
       <c r="J103" s="4" t="inlineStr">
@@ -5131,13 +5193,13 @@
           <t>PERSONAS PARROQUIA</t>
         </is>
       </c>
-      <c r="G104" s="7" t="n">
+      <c r="G104" s="5" t="n">
         <v>1133</v>
       </c>
-      <c r="H104" s="7" t="n">
+      <c r="H104" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="I104" s="7" t="n">
+      <c r="I104" s="5" t="n">
         <v>32771</v>
       </c>
       <c r="J104" s="4" t="inlineStr">
@@ -5178,13 +5240,13 @@
           <t>Discapacidad Voz y Habla</t>
         </is>
       </c>
-      <c r="G105" s="7" t="n">
+      <c r="G105" s="5" t="n">
         <v>1148</v>
       </c>
-      <c r="H105" s="7" t="n">
+      <c r="H105" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="I105" s="7" t="n">
+      <c r="I105" s="5" t="n">
         <v>7910</v>
       </c>
       <c r="J105" s="4" t="inlineStr">
@@ -5225,13 +5287,13 @@
           <t>Exportaciones Capítulo</t>
         </is>
       </c>
-      <c r="G106" s="7" t="n">
+      <c r="G106" s="5" t="n">
         <v>107</v>
       </c>
-      <c r="H106" s="7" t="n">
+      <c r="H106" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="I106" s="7" t="n">
+      <c r="I106" s="5" t="n">
         <v>2132</v>
       </c>
       <c r="J106" s="4" t="inlineStr">
@@ -5272,13 +5334,13 @@
           <t>Importaciones Capítulo</t>
         </is>
       </c>
-      <c r="G107" s="7" t="n">
+      <c r="G107" s="5" t="n">
         <v>107</v>
       </c>
-      <c r="H107" s="7" t="n">
+      <c r="H107" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="I107" s="7" t="n">
+      <c r="I107" s="5" t="n">
         <v>2182</v>
       </c>
       <c r="J107" s="4" t="inlineStr">
@@ -5319,13 +5381,13 @@
           <t>NACIONAL</t>
         </is>
       </c>
-      <c r="G108" s="7" t="n">
+      <c r="G108" s="5" t="n">
         <v>776</v>
       </c>
-      <c r="H108" s="7" t="n">
+      <c r="H108" s="5" t="n">
         <v>49</v>
       </c>
-      <c r="I108" s="7" t="n">
+      <c r="I108" s="5" t="n">
         <v>29868</v>
       </c>
       <c r="J108" s="4" t="inlineStr">
@@ -5366,13 +5428,13 @@
           <t>NBI</t>
         </is>
       </c>
-      <c r="G109" s="7" t="n">
+      <c r="G109" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="H109" s="7" t="n">
+      <c r="H109" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="I109" s="7" t="n">
+      <c r="I109" s="5" t="n">
         <v>300</v>
       </c>
       <c r="J109" s="4" t="inlineStr">
@@ -5413,13 +5475,13 @@
           <t>NBI</t>
         </is>
       </c>
-      <c r="G110" s="7" t="n">
+      <c r="G110" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="H110" s="7" t="n">
+      <c r="H110" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="I110" s="7" t="n">
+      <c r="I110" s="5" t="n">
         <v>165</v>
       </c>
       <c r="J110" s="4" t="inlineStr">
@@ -5460,13 +5522,13 @@
           <t>DIVORCIOS</t>
         </is>
       </c>
-      <c r="G111" s="7" t="n">
+      <c r="G111" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="H111" s="7" t="n">
+      <c r="H111" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="I111" s="7" t="n">
+      <c r="I111" s="5" t="n">
         <v>602</v>
       </c>
       <c r="J111" s="4" t="inlineStr">
@@ -5507,13 +5569,13 @@
           <t>DEFUNCIONES</t>
         </is>
       </c>
-      <c r="G112" s="7" t="n">
+      <c r="G112" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="H112" s="7" t="n">
+      <c r="H112" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="I112" s="7" t="n">
+      <c r="I112" s="5" t="n">
         <v>630</v>
       </c>
       <c r="J112" s="4" t="inlineStr">
@@ -5554,13 +5616,13 @@
           <t>MATRIMONIOS</t>
         </is>
       </c>
-      <c r="G113" s="7" t="n">
+      <c r="G113" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="H113" s="7" t="n">
+      <c r="H113" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="I113" s="7" t="n">
+      <c r="I113" s="5" t="n">
         <v>602</v>
       </c>
       <c r="J113" s="4" t="inlineStr">
@@ -5601,13 +5663,13 @@
           <t>NACIMIENTOS</t>
         </is>
       </c>
-      <c r="G114" s="7" t="n">
+      <c r="G114" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="H114" s="7" t="n">
+      <c r="H114" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="I114" s="7" t="n">
+      <c r="I114" s="5" t="n">
         <v>628</v>
       </c>
       <c r="J114" s="4" t="inlineStr">
@@ -5648,13 +5710,13 @@
           <t>DEFUNCIONES</t>
         </is>
       </c>
-      <c r="G115" s="7" t="n">
+      <c r="G115" s="5" t="n">
         <v>409</v>
       </c>
-      <c r="H115" s="7" t="n">
+      <c r="H115" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="I115" s="7" t="n">
+      <c r="I115" s="5" t="n">
         <v>2388</v>
       </c>
       <c r="J115" s="4" t="inlineStr">
@@ -5695,13 +5757,13 @@
           <t>MATRIMONIOS</t>
         </is>
       </c>
-      <c r="G116" s="7" t="n">
+      <c r="G116" s="5" t="n">
         <v>373</v>
       </c>
-      <c r="H116" s="7" t="n">
+      <c r="H116" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="I116" s="7" t="n">
+      <c r="I116" s="5" t="n">
         <v>2178</v>
       </c>
       <c r="J116" s="4" t="inlineStr">
@@ -5742,13 +5804,13 @@
           <t>NACIMIENTOS</t>
         </is>
       </c>
-      <c r="G117" s="7" t="n">
+      <c r="G117" s="5" t="n">
         <v>407</v>
       </c>
-      <c r="H117" s="7" t="n">
+      <c r="H117" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="I117" s="7" t="n">
+      <c r="I117" s="5" t="n">
         <v>2377</v>
       </c>
       <c r="J117" s="4" t="inlineStr">
@@ -5789,13 +5851,13 @@
           <t>SUICIDIOS</t>
         </is>
       </c>
-      <c r="G118" s="7" t="n">
+      <c r="G118" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="H118" s="7" t="n">
+      <c r="H118" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="I118" s="7" t="n">
+      <c r="I118" s="5" t="n">
         <v>603</v>
       </c>
       <c r="J118" s="4" t="inlineStr">
@@ -5836,13 +5898,13 @@
           <t>n_CEN</t>
         </is>
       </c>
-      <c r="G119" s="7" t="n">
+      <c r="G119" s="5" t="n">
         <v>666</v>
       </c>
-      <c r="H119" s="7" t="n">
+      <c r="H119" s="5" t="n">
         <v>77</v>
       </c>
-      <c r="I119" s="7" t="n">
+      <c r="I119" s="5" t="n">
         <v>50624</v>
       </c>
       <c r="J119" s="4" t="inlineStr">
@@ -5883,13 +5945,13 @@
           <t>Estado Amazonas</t>
         </is>
       </c>
-      <c r="G120" s="7" t="n">
+      <c r="G120" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="H120" s="7" t="n">
+      <c r="H120" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="I120" s="7" t="n">
+      <c r="I120" s="5" t="n">
         <v>1303</v>
       </c>
       <c r="J120" s="4" t="inlineStr">
@@ -5930,13 +5992,13 @@
           <t>Estado Amazonas</t>
         </is>
       </c>
-      <c r="G121" s="7" t="n">
+      <c r="G121" s="5" t="n">
         <v>78</v>
       </c>
-      <c r="H121" s="7" t="n">
+      <c r="H121" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="I121" s="7" t="n">
+      <c r="I121" s="5" t="n">
         <v>807</v>
       </c>
       <c r="J121" s="4" t="inlineStr">
@@ -5977,13 +6039,13 @@
           <t>Estado Amazonas</t>
         </is>
       </c>
-      <c r="G122" s="7" t="n">
+      <c r="G122" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="H122" s="7" t="n">
+      <c r="H122" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="I122" s="7" t="n">
+      <c r="I122" s="5" t="n">
         <v>1303</v>
       </c>
       <c r="J122" s="4" t="inlineStr">
@@ -6024,13 +6086,13 @@
           <t>n_CEN</t>
         </is>
       </c>
-      <c r="G123" s="7" t="n">
+      <c r="G123" s="5" t="n">
         <v>1384</v>
       </c>
-      <c r="H123" s="7" t="n">
+      <c r="H123" s="5" t="n">
         <v>77</v>
       </c>
-      <c r="I123" s="7" t="n">
+      <c r="I123" s="5" t="n">
         <v>105211</v>
       </c>
       <c r="J123" s="4" t="inlineStr">
@@ -6071,13 +6133,13 @@
           <t>Estado Anzoátegui</t>
         </is>
       </c>
-      <c r="G124" s="7" t="n">
+      <c r="G124" s="5" t="n">
         <v>78</v>
       </c>
-      <c r="H124" s="7" t="n">
+      <c r="H124" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="I124" s="7" t="n">
+      <c r="I124" s="5" t="n">
         <v>3487</v>
       </c>
       <c r="J124" s="4" t="inlineStr">
@@ -6118,13 +6180,13 @@
           <t>Estado Anzoátegui</t>
         </is>
       </c>
-      <c r="G125" s="7" t="n">
+      <c r="G125" s="5" t="n">
         <v>78</v>
       </c>
-      <c r="H125" s="7" t="n">
+      <c r="H125" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="I125" s="7" t="n">
+      <c r="I125" s="5" t="n">
         <v>807</v>
       </c>
       <c r="J125" s="4" t="inlineStr">
@@ -6165,13 +6227,13 @@
           <t>Estado Anzoátegui</t>
         </is>
       </c>
-      <c r="G126" s="7" t="n">
+      <c r="G126" s="5" t="n">
         <v>78</v>
       </c>
-      <c r="H126" s="7" t="n">
+      <c r="H126" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="I126" s="7" t="n">
+      <c r="I126" s="5" t="n">
         <v>3487</v>
       </c>
       <c r="J126" s="4" t="inlineStr">
@@ -6212,13 +6274,13 @@
           <t>n_CEN</t>
         </is>
       </c>
-      <c r="G127" s="7" t="n">
+      <c r="G127" s="5" t="n">
         <v>1392</v>
       </c>
-      <c r="H127" s="7" t="n">
+      <c r="H127" s="5" t="n">
         <v>77</v>
       </c>
-      <c r="I127" s="7" t="n">
+      <c r="I127" s="5" t="n">
         <v>105839</v>
       </c>
       <c r="J127" s="4" t="inlineStr">
@@ -6259,13 +6321,13 @@
           <t>Estado Apure</t>
         </is>
       </c>
-      <c r="G128" s="7" t="n">
+      <c r="G128" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="H128" s="7" t="n">
+      <c r="H128" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="I128" s="7" t="n">
+      <c r="I128" s="5" t="n">
         <v>1303</v>
       </c>
       <c r="J128" s="4" t="inlineStr">
@@ -6306,13 +6368,13 @@
           <t>Estado Apure</t>
         </is>
       </c>
-      <c r="G129" s="7" t="n">
+      <c r="G129" s="5" t="n">
         <v>78</v>
       </c>
-      <c r="H129" s="7" t="n">
+      <c r="H129" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="I129" s="7" t="n">
+      <c r="I129" s="5" t="n">
         <v>807</v>
       </c>
       <c r="J129" s="4" t="inlineStr">
@@ -6353,13 +6415,13 @@
           <t>Estado Apure</t>
         </is>
       </c>
-      <c r="G130" s="7" t="n">
+      <c r="G130" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="H130" s="7" t="n">
+      <c r="H130" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="I130" s="7" t="n">
+      <c r="I130" s="5" t="n">
         <v>1303</v>
       </c>
       <c r="J130" s="4" t="inlineStr">
@@ -6400,13 +6462,13 @@
           <t>n_CEN</t>
         </is>
       </c>
-      <c r="G131" s="7" t="n">
+      <c r="G131" s="5" t="n">
         <v>2011</v>
       </c>
-      <c r="H131" s="7" t="n">
+      <c r="H131" s="5" t="n">
         <v>77</v>
       </c>
-      <c r="I131" s="7" t="n">
+      <c r="I131" s="5" t="n">
         <v>152836</v>
       </c>
       <c r="J131" s="4" t="inlineStr">
@@ -6447,13 +6509,13 @@
           <t>Estado Barinas</t>
         </is>
       </c>
-      <c r="G132" s="7" t="n">
+      <c r="G132" s="5" t="n">
         <v>51</v>
       </c>
-      <c r="H132" s="7" t="n">
+      <c r="H132" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="I132" s="7" t="n">
+      <c r="I132" s="5" t="n">
         <v>2083</v>
       </c>
       <c r="J132" s="4" t="inlineStr">
@@ -6494,13 +6556,13 @@
           <t>Estado Barinas</t>
         </is>
       </c>
-      <c r="G133" s="7" t="n">
+      <c r="G133" s="5" t="n">
         <v>78</v>
       </c>
-      <c r="H133" s="7" t="n">
+      <c r="H133" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="I133" s="7" t="n">
+      <c r="I133" s="5" t="n">
         <v>807</v>
       </c>
       <c r="J133" s="4" t="inlineStr">
@@ -6541,13 +6603,13 @@
           <t>Estado Barinas</t>
         </is>
       </c>
-      <c r="G134" s="7" t="n">
+      <c r="G134" s="5" t="n">
         <v>51</v>
       </c>
-      <c r="H134" s="7" t="n">
+      <c r="H134" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="I134" s="7" t="n">
+      <c r="I134" s="5" t="n">
         <v>2083</v>
       </c>
       <c r="J134" s="4" t="inlineStr">
@@ -6588,13 +6650,13 @@
           <t>n_CEN</t>
         </is>
       </c>
-      <c r="G135" s="7" t="n">
+      <c r="G135" s="5" t="n">
         <v>1810</v>
       </c>
-      <c r="H135" s="7" t="n">
+      <c r="H135" s="5" t="n">
         <v>77</v>
       </c>
-      <c r="I135" s="7" t="n">
+      <c r="I135" s="5" t="n">
         <v>137582</v>
       </c>
       <c r="J135" s="4" t="inlineStr">
@@ -6635,13 +6697,13 @@
           <t>Estado Bolívar</t>
         </is>
       </c>
-      <c r="G136" s="7" t="n">
+      <c r="G136" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="H136" s="7" t="n">
+      <c r="H136" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="I136" s="7" t="n">
+      <c r="I136" s="5" t="n">
         <v>1927</v>
       </c>
       <c r="J136" s="4" t="inlineStr">
@@ -6682,13 +6744,13 @@
           <t>Estado Bolívar</t>
         </is>
       </c>
-      <c r="G137" s="7" t="n">
+      <c r="G137" s="5" t="n">
         <v>78</v>
       </c>
-      <c r="H137" s="7" t="n">
+      <c r="H137" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="I137" s="7" t="n">
+      <c r="I137" s="5" t="n">
         <v>807</v>
       </c>
       <c r="J137" s="4" t="inlineStr">
@@ -6729,13 +6791,13 @@
           <t>Estado Bolívar</t>
         </is>
       </c>
-      <c r="G138" s="7" t="n">
+      <c r="G138" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="H138" s="7" t="n">
+      <c r="H138" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="I138" s="7" t="n">
+      <c r="I138" s="5" t="n">
         <v>1927</v>
       </c>
       <c r="J138" s="4" t="inlineStr">
@@ -6776,13 +6838,13 @@
           <t>n_CEN</t>
         </is>
       </c>
-      <c r="G139" s="7" t="n">
+      <c r="G139" s="5" t="n">
         <v>388</v>
       </c>
-      <c r="H139" s="7" t="n">
+      <c r="H139" s="5" t="n">
         <v>77</v>
       </c>
-      <c r="I139" s="7" t="n">
+      <c r="I139" s="5" t="n">
         <v>29489</v>
       </c>
       <c r="J139" s="4" t="inlineStr">
@@ -6823,13 +6885,13 @@
           <t>Estado Carabobo</t>
         </is>
       </c>
-      <c r="G140" s="7" t="n">
+      <c r="G140" s="5" t="n">
         <v>57</v>
       </c>
-      <c r="H140" s="7" t="n">
+      <c r="H140" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="I140" s="7" t="n">
+      <c r="I140" s="5" t="n">
         <v>2395</v>
       </c>
       <c r="J140" s="4" t="inlineStr">
@@ -6870,13 +6932,13 @@
           <t>Estado Carabobo</t>
         </is>
       </c>
-      <c r="G141" s="7" t="n">
+      <c r="G141" s="5" t="n">
         <v>78</v>
       </c>
-      <c r="H141" s="7" t="n">
+      <c r="H141" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="I141" s="7" t="n">
+      <c r="I141" s="5" t="n">
         <v>807</v>
       </c>
       <c r="J141" s="4" t="inlineStr">
@@ -6917,13 +6979,13 @@
           <t>Estado Carabobo</t>
         </is>
       </c>
-      <c r="G142" s="7" t="n">
+      <c r="G142" s="5" t="n">
         <v>57</v>
       </c>
-      <c r="H142" s="7" t="n">
+      <c r="H142" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="I142" s="7" t="n">
+      <c r="I142" s="5" t="n">
         <v>2395</v>
       </c>
       <c r="J142" s="4" t="inlineStr">
@@ -6964,13 +7026,13 @@
           <t>n_CEN</t>
         </is>
       </c>
-      <c r="G143" s="7" t="n">
+      <c r="G143" s="5" t="n">
         <v>537</v>
       </c>
-      <c r="H143" s="7" t="n">
+      <c r="H143" s="5" t="n">
         <v>77</v>
       </c>
-      <c r="I143" s="7" t="n">
+      <c r="I143" s="5" t="n">
         <v>40813</v>
       </c>
       <c r="J143" s="4" t="inlineStr">
@@ -7011,13 +7073,13 @@
           <t>Estado Cojedes</t>
         </is>
       </c>
-      <c r="G144" s="7" t="n">
+      <c r="G144" s="5" t="n">
         <v>42</v>
       </c>
-      <c r="H144" s="7" t="n">
+      <c r="H144" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="I144" s="7" t="n">
+      <c r="I144" s="5" t="n">
         <v>1615</v>
       </c>
       <c r="J144" s="4" t="inlineStr">
@@ -7058,13 +7120,13 @@
           <t>Estado Cojedes</t>
         </is>
       </c>
-      <c r="G145" s="7" t="n">
+      <c r="G145" s="5" t="n">
         <v>78</v>
       </c>
-      <c r="H145" s="7" t="n">
+      <c r="H145" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="I145" s="7" t="n">
+      <c r="I145" s="5" t="n">
         <v>807</v>
       </c>
       <c r="J145" s="4" t="inlineStr">
@@ -7105,13 +7167,13 @@
           <t>Estado Cojedes</t>
         </is>
       </c>
-      <c r="G146" s="7" t="n">
+      <c r="G146" s="5" t="n">
         <v>42</v>
       </c>
-      <c r="H146" s="7" t="n">
+      <c r="H146" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="I146" s="7" t="n">
+      <c r="I146" s="5" t="n">
         <v>1615</v>
       </c>
       <c r="J146" s="4" t="inlineStr">
@@ -7152,13 +7214,13 @@
           <t>n_CEN</t>
         </is>
       </c>
-      <c r="G147" s="7" t="n">
+      <c r="G147" s="5" t="n">
         <v>587</v>
       </c>
-      <c r="H147" s="7" t="n">
+      <c r="H147" s="5" t="n">
         <v>77</v>
       </c>
-      <c r="I147" s="7" t="n">
+      <c r="I147" s="5" t="n">
         <v>44626</v>
       </c>
       <c r="J147" s="4" t="inlineStr">
@@ -7199,13 +7261,13 @@
           <t>Estado Delta Amacuro</t>
         </is>
       </c>
-      <c r="G148" s="7" t="n">
+      <c r="G148" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="H148" s="7" t="n">
+      <c r="H148" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="I148" s="7" t="n">
+      <c r="I148" s="5" t="n">
         <v>835</v>
       </c>
       <c r="J148" s="4" t="inlineStr">
@@ -7246,13 +7308,13 @@
           <t>Estado Delta Amacuro</t>
         </is>
       </c>
-      <c r="G149" s="7" t="n">
+      <c r="G149" s="5" t="n">
         <v>78</v>
       </c>
-      <c r="H149" s="7" t="n">
+      <c r="H149" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="I149" s="7" t="n">
+      <c r="I149" s="5" t="n">
         <v>807</v>
       </c>
       <c r="J149" s="4" t="inlineStr">
@@ -7293,13 +7355,13 @@
           <t>Estado Delta Amacuro</t>
         </is>
       </c>
-      <c r="G150" s="7" t="n">
+      <c r="G150" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="H150" s="7" t="n">
+      <c r="H150" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="I150" s="7" t="n">
+      <c r="I150" s="5" t="n">
         <v>835</v>
       </c>
       <c r="J150" s="4" t="inlineStr">
@@ -7340,13 +7402,13 @@
           <t>Dependencias Federales</t>
         </is>
       </c>
-      <c r="G151" s="7" t="n">
+      <c r="G151" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="H151" s="7" t="n">
+      <c r="H151" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="I151" s="7" t="n">
+      <c r="I151" s="5" t="n">
         <v>211</v>
       </c>
       <c r="J151" s="4" t="inlineStr">
@@ -7387,13 +7449,13 @@
           <t>Dependencias Federales</t>
         </is>
       </c>
-      <c r="G152" s="7" t="n">
+      <c r="G152" s="5" t="n">
         <v>78</v>
       </c>
-      <c r="H152" s="7" t="n">
+      <c r="H152" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="I152" s="7" t="n">
+      <c r="I152" s="5" t="n">
         <v>807</v>
       </c>
       <c r="J152" s="4" t="inlineStr">
@@ -7434,13 +7496,13 @@
           <t>Dependencias Federales</t>
         </is>
       </c>
-      <c r="G153" s="7" t="n">
+      <c r="G153" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="H153" s="7" t="n">
+      <c r="H153" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="I153" s="7" t="n">
+      <c r="I153" s="5" t="n">
         <v>211</v>
       </c>
       <c r="J153" s="4" t="inlineStr">
@@ -7481,13 +7543,13 @@
           <t>Distrito Capital</t>
         </is>
       </c>
-      <c r="G154" s="7" t="n">
+      <c r="G154" s="5" t="n">
         <v>81</v>
       </c>
-      <c r="H154" s="7" t="n">
+      <c r="H154" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="I154" s="7" t="n">
+      <c r="I154" s="5" t="n">
         <v>3643</v>
       </c>
       <c r="J154" s="4" t="inlineStr">
@@ -7528,13 +7590,13 @@
           <t>n_CEN</t>
         </is>
       </c>
-      <c r="G155" s="7" t="n">
+      <c r="G155" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="H155" s="7" t="n">
+      <c r="H155" s="5" t="n">
         <v>77</v>
       </c>
-      <c r="I155" s="7" t="n">
+      <c r="I155" s="5" t="n">
         <v>2205</v>
       </c>
       <c r="J155" s="4" t="inlineStr">
@@ -7575,13 +7637,13 @@
           <t>Distrito Capital</t>
         </is>
       </c>
-      <c r="G156" s="7" t="n">
+      <c r="G156" s="5" t="n">
         <v>78</v>
       </c>
-      <c r="H156" s="7" t="n">
+      <c r="H156" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="I156" s="7" t="n">
+      <c r="I156" s="5" t="n">
         <v>807</v>
       </c>
       <c r="J156" s="4" t="inlineStr">
@@ -7622,13 +7684,13 @@
           <t>Distrito Capital</t>
         </is>
       </c>
-      <c r="G157" s="7" t="n">
+      <c r="G157" s="5" t="n">
         <v>81</v>
       </c>
-      <c r="H157" s="7" t="n">
+      <c r="H157" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="I157" s="7" t="n">
+      <c r="I157" s="5" t="n">
         <v>3643</v>
       </c>
       <c r="J157" s="4" t="inlineStr">
@@ -7669,13 +7731,13 @@
           <t>Estado Falcón</t>
         </is>
       </c>
-      <c r="G158" s="7" t="n">
+      <c r="G158" s="5" t="n">
         <v>90</v>
       </c>
-      <c r="H158" s="7" t="n">
+      <c r="H158" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="I158" s="7" t="n">
+      <c r="I158" s="5" t="n">
         <v>4111</v>
       </c>
       <c r="J158" s="4" t="inlineStr">
@@ -7716,13 +7778,13 @@
           <t>Estado Falcón</t>
         </is>
       </c>
-      <c r="G159" s="7" t="n">
+      <c r="G159" s="5" t="n">
         <v>78</v>
       </c>
-      <c r="H159" s="7" t="n">
+      <c r="H159" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="I159" s="7" t="n">
+      <c r="I159" s="5" t="n">
         <v>807</v>
       </c>
       <c r="J159" s="4" t="inlineStr">
@@ -7763,13 +7825,13 @@
           <t>Estado Falcón</t>
         </is>
       </c>
-      <c r="G160" s="7" t="n">
+      <c r="G160" s="5" t="n">
         <v>90</v>
       </c>
-      <c r="H160" s="7" t="n">
+      <c r="H160" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="I160" s="7" t="n">
+      <c r="I160" s="5" t="n">
         <v>4111</v>
       </c>
       <c r="J160" s="4" t="inlineStr">
@@ -7810,13 +7872,13 @@
           <t>n_CEN</t>
         </is>
       </c>
-      <c r="G161" s="7" t="n">
+      <c r="G161" s="5" t="n">
         <v>2086</v>
       </c>
-      <c r="H161" s="7" t="n">
+      <c r="H161" s="5" t="n">
         <v>77</v>
       </c>
-      <c r="I161" s="7" t="n">
+      <c r="I161" s="5" t="n">
         <v>158537</v>
       </c>
       <c r="J161" s="4" t="inlineStr">
@@ -7857,13 +7919,13 @@
           <t>Estado Guárico</t>
         </is>
       </c>
-      <c r="G162" s="7" t="n">
+      <c r="G162" s="5" t="n">
         <v>60</v>
       </c>
-      <c r="H162" s="7" t="n">
+      <c r="H162" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="I162" s="7" t="n">
+      <c r="I162" s="5" t="n">
         <v>2551</v>
       </c>
       <c r="J162" s="4" t="inlineStr">
@@ -7904,13 +7966,13 @@
           <t>Estado Guárico</t>
         </is>
       </c>
-      <c r="G163" s="7" t="n">
+      <c r="G163" s="5" t="n">
         <v>78</v>
       </c>
-      <c r="H163" s="7" t="n">
+      <c r="H163" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="I163" s="7" t="n">
+      <c r="I163" s="5" t="n">
         <v>807</v>
       </c>
       <c r="J163" s="4" t="inlineStr">
@@ -7951,13 +8013,13 @@
           <t>Estado Guárico</t>
         </is>
       </c>
-      <c r="G164" s="7" t="n">
+      <c r="G164" s="5" t="n">
         <v>60</v>
       </c>
-      <c r="H164" s="7" t="n">
+      <c r="H164" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="I164" s="7" t="n">
+      <c r="I164" s="5" t="n">
         <v>2551</v>
       </c>
       <c r="J164" s="4" t="inlineStr">
@@ -7998,13 +8060,13 @@
           <t>n_CEN</t>
         </is>
       </c>
-      <c r="G165" s="7" t="n">
+      <c r="G165" s="5" t="n">
         <v>2450</v>
       </c>
-      <c r="H165" s="7" t="n">
+      <c r="H165" s="5" t="n">
         <v>77</v>
       </c>
-      <c r="I165" s="7" t="n">
+      <c r="I165" s="5" t="n">
         <v>186201</v>
       </c>
       <c r="J165" s="4" t="inlineStr">
@@ -8045,13 +8107,13 @@
           <t>Estado Vargas</t>
         </is>
       </c>
-      <c r="G166" s="7" t="n">
+      <c r="G166" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="H166" s="7" t="n">
+      <c r="H166" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="I166" s="7" t="n">
+      <c r="I166" s="5" t="n">
         <v>1927</v>
       </c>
       <c r="J166" s="4" t="inlineStr">
@@ -8092,13 +8154,13 @@
           <t>Estado Vargas</t>
         </is>
       </c>
-      <c r="G167" s="7" t="n">
+      <c r="G167" s="5" t="n">
         <v>78</v>
       </c>
-      <c r="H167" s="7" t="n">
+      <c r="H167" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="I167" s="7" t="n">
+      <c r="I167" s="5" t="n">
         <v>807</v>
       </c>
       <c r="J167" s="4" t="inlineStr">
@@ -8139,13 +8201,13 @@
           <t>Estado Vargas</t>
         </is>
       </c>
-      <c r="G168" s="7" t="n">
+      <c r="G168" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="H168" s="7" t="n">
+      <c r="H168" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="I168" s="7" t="n">
+      <c r="I168" s="5" t="n">
         <v>1927</v>
       </c>
       <c r="J168" s="4" t="inlineStr">
@@ -8186,13 +8248,13 @@
           <t>n_CEN</t>
         </is>
       </c>
-      <c r="G169" s="7" t="n">
+      <c r="G169" s="5" t="n">
         <v>164</v>
       </c>
-      <c r="H169" s="7" t="n">
+      <c r="H169" s="5" t="n">
         <v>77</v>
       </c>
-      <c r="I169" s="7" t="n">
+      <c r="I169" s="5" t="n">
         <v>12465</v>
       </c>
       <c r="J169" s="4" t="inlineStr">
@@ -8233,13 +8295,13 @@
           <t>Indice de Masculinidad ENT</t>
         </is>
       </c>
-      <c r="G170" s="7" t="n">
+      <c r="G170" s="5" t="n">
         <v>86</v>
       </c>
-      <c r="H170" s="7" t="n">
+      <c r="H170" s="5" t="n">
         <v>55</v>
       </c>
-      <c r="I170" s="7" t="n">
+      <c r="I170" s="5" t="n">
         <v>4159</v>
       </c>
       <c r="J170" s="4" t="inlineStr">
@@ -8280,13 +8342,13 @@
           <t>Estado Lara</t>
         </is>
       </c>
-      <c r="G171" s="7" t="n">
+      <c r="G171" s="5" t="n">
         <v>42</v>
       </c>
-      <c r="H171" s="7" t="n">
+      <c r="H171" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="I171" s="7" t="n">
+      <c r="I171" s="5" t="n">
         <v>1615</v>
       </c>
       <c r="J171" s="4" t="inlineStr">
@@ -8327,13 +8389,13 @@
           <t>Estado Lara</t>
         </is>
       </c>
-      <c r="G172" s="7" t="n">
+      <c r="G172" s="5" t="n">
         <v>78</v>
       </c>
-      <c r="H172" s="7" t="n">
+      <c r="H172" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="I172" s="7" t="n">
+      <c r="I172" s="5" t="n">
         <v>807</v>
       </c>
       <c r="J172" s="4" t="inlineStr">
@@ -8374,13 +8436,13 @@
           <t>Indice de Masculinidad ENT</t>
         </is>
       </c>
-      <c r="G173" s="7" t="n">
+      <c r="G173" s="5" t="n">
         <v>86</v>
       </c>
-      <c r="H173" s="7" t="n">
+      <c r="H173" s="5" t="n">
         <v>55</v>
       </c>
-      <c r="I173" s="7" t="n">
+      <c r="I173" s="5" t="n">
         <v>4159</v>
       </c>
       <c r="J173" s="4" t="inlineStr">
@@ -8421,13 +8483,13 @@
           <t>Estado Lara</t>
         </is>
       </c>
-      <c r="G174" s="7" t="n">
+      <c r="G174" s="5" t="n">
         <v>42</v>
       </c>
-      <c r="H174" s="7" t="n">
+      <c r="H174" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="I174" s="7" t="n">
+      <c r="I174" s="5" t="n">
         <v>1615</v>
       </c>
       <c r="J174" s="4" t="inlineStr">
@@ -8468,13 +8530,13 @@
           <t>n_CEN</t>
         </is>
       </c>
-      <c r="G175" s="7" t="n">
+      <c r="G175" s="5" t="n">
         <v>2231</v>
       </c>
-      <c r="H175" s="7" t="n">
+      <c r="H175" s="5" t="n">
         <v>77</v>
       </c>
-      <c r="I175" s="7" t="n">
+      <c r="I175" s="5" t="n">
         <v>169557</v>
       </c>
       <c r="J175" s="4" t="inlineStr">
@@ -8515,13 +8577,13 @@
           <t>Estado Miranda</t>
         </is>
       </c>
-      <c r="G176" s="7" t="n">
+      <c r="G176" s="5" t="n">
         <v>78</v>
       </c>
-      <c r="H176" s="7" t="n">
+      <c r="H176" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="I176" s="7" t="n">
+      <c r="I176" s="5" t="n">
         <v>3487</v>
       </c>
       <c r="J176" s="4" t="inlineStr">
@@ -8562,13 +8624,13 @@
           <t>Estado Miranda</t>
         </is>
       </c>
-      <c r="G177" s="7" t="n">
+      <c r="G177" s="5" t="n">
         <v>78</v>
       </c>
-      <c r="H177" s="7" t="n">
+      <c r="H177" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="I177" s="7" t="n">
+      <c r="I177" s="5" t="n">
         <v>807</v>
       </c>
       <c r="J177" s="4" t="inlineStr">
@@ -8609,13 +8671,13 @@
           <t>Estado Miranda</t>
         </is>
       </c>
-      <c r="G178" s="7" t="n">
+      <c r="G178" s="5" t="n">
         <v>78</v>
       </c>
-      <c r="H178" s="7" t="n">
+      <c r="H178" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="I178" s="7" t="n">
+      <c r="I178" s="5" t="n">
         <v>3487</v>
       </c>
       <c r="J178" s="4" t="inlineStr">
@@ -8656,13 +8718,13 @@
           <t>n_CEN</t>
         </is>
       </c>
-      <c r="G179" s="7" t="n">
+      <c r="G179" s="5" t="n">
         <v>699</v>
       </c>
-      <c r="H179" s="7" t="n">
+      <c r="H179" s="5" t="n">
         <v>77</v>
       </c>
-      <c r="I179" s="7" t="n">
+      <c r="I179" s="5" t="n">
         <v>53125</v>
       </c>
       <c r="J179" s="4" t="inlineStr">
@@ -8703,13 +8765,13 @@
           <t>Estado Monagas</t>
         </is>
       </c>
-      <c r="G180" s="7" t="n">
+      <c r="G180" s="5" t="n">
         <v>54</v>
       </c>
-      <c r="H180" s="7" t="n">
+      <c r="H180" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="I180" s="7" t="n">
+      <c r="I180" s="5" t="n">
         <v>2239</v>
       </c>
       <c r="J180" s="4" t="inlineStr">
@@ -8750,13 +8812,13 @@
           <t>Estado Monagas</t>
         </is>
       </c>
-      <c r="G181" s="7" t="n">
+      <c r="G181" s="5" t="n">
         <v>78</v>
       </c>
-      <c r="H181" s="7" t="n">
+      <c r="H181" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="I181" s="7" t="n">
+      <c r="I181" s="5" t="n">
         <v>807</v>
       </c>
       <c r="J181" s="4" t="inlineStr">
@@ -8797,13 +8859,13 @@
           <t>Estado Monagas</t>
         </is>
       </c>
-      <c r="G182" s="7" t="n">
+      <c r="G182" s="5" t="n">
         <v>54</v>
       </c>
-      <c r="H182" s="7" t="n">
+      <c r="H182" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="I182" s="7" t="n">
+      <c r="I182" s="5" t="n">
         <v>2239</v>
       </c>
       <c r="J182" s="4" t="inlineStr">
@@ -8844,13 +8906,13 @@
           <t>n_CEN</t>
         </is>
       </c>
-      <c r="G183" s="7" t="n">
+      <c r="G183" s="5" t="n">
         <v>796</v>
       </c>
-      <c r="H183" s="7" t="n">
+      <c r="H183" s="5" t="n">
         <v>77</v>
       </c>
-      <c r="I183" s="7" t="n">
+      <c r="I183" s="5" t="n">
         <v>60507</v>
       </c>
       <c r="J183" s="4" t="inlineStr">
@@ -8891,13 +8953,13 @@
           <t>Estado Mérida</t>
         </is>
       </c>
-      <c r="G184" s="7" t="n">
+      <c r="G184" s="5" t="n">
         <v>84</v>
       </c>
-      <c r="H184" s="7" t="n">
+      <c r="H184" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="I184" s="7" t="n">
+      <c r="I184" s="5" t="n">
         <v>3799</v>
       </c>
       <c r="J184" s="4" t="inlineStr">
@@ -8938,13 +9000,13 @@
           <t>Estado Mérida</t>
         </is>
       </c>
-      <c r="G185" s="7" t="n">
+      <c r="G185" s="5" t="n">
         <v>78</v>
       </c>
-      <c r="H185" s="7" t="n">
+      <c r="H185" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="I185" s="7" t="n">
+      <c r="I185" s="5" t="n">
         <v>807</v>
       </c>
       <c r="J185" s="4" t="inlineStr">
@@ -8985,13 +9047,13 @@
           <t>Estado Mérida</t>
         </is>
       </c>
-      <c r="G186" s="7" t="n">
+      <c r="G186" s="5" t="n">
         <v>84</v>
       </c>
-      <c r="H186" s="7" t="n">
+      <c r="H186" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="I186" s="7" t="n">
+      <c r="I186" s="5" t="n">
         <v>3799</v>
       </c>
       <c r="J186" s="4" t="inlineStr">
@@ -9032,13 +9094,13 @@
           <t>n_CEN</t>
         </is>
       </c>
-      <c r="G187" s="7" t="n">
+      <c r="G187" s="5" t="n">
         <v>1649</v>
       </c>
-      <c r="H187" s="7" t="n">
+      <c r="H187" s="5" t="n">
         <v>77</v>
       </c>
-      <c r="I187" s="7" t="n">
+      <c r="I187" s="5" t="n">
         <v>125325</v>
       </c>
       <c r="J187" s="4" t="inlineStr">
@@ -9079,13 +9141,13 @@
           <t>Resumen Entidad</t>
         </is>
       </c>
-      <c r="G188" s="7" t="n">
+      <c r="G188" s="5" t="n">
         <v>93</v>
       </c>
-      <c r="H188" s="7" t="n">
+      <c r="H188" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="I188" s="7" t="n">
+      <c r="I188" s="5" t="n">
         <v>4113</v>
       </c>
       <c r="J188" s="4" t="inlineStr">
@@ -9126,13 +9188,13 @@
           <t>Nacional</t>
         </is>
       </c>
-      <c r="G189" s="7" t="n">
+      <c r="G189" s="5" t="n">
         <v>78</v>
       </c>
-      <c r="H189" s="7" t="n">
+      <c r="H189" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="I189" s="7" t="n">
+      <c r="I189" s="5" t="n">
         <v>807</v>
       </c>
       <c r="J189" s="4" t="inlineStr">
@@ -9173,13 +9235,13 @@
           <t>Indice de Masculinidad ENT</t>
         </is>
       </c>
-      <c r="G190" s="7" t="n">
+      <c r="G190" s="5" t="n">
         <v>86</v>
       </c>
-      <c r="H190" s="7" t="n">
+      <c r="H190" s="5" t="n">
         <v>55</v>
       </c>
-      <c r="I190" s="7" t="n">
+      <c r="I190" s="5" t="n">
         <v>4159</v>
       </c>
       <c r="J190" s="4" t="inlineStr">
@@ -9220,13 +9282,13 @@
           <t>Estado Nueva Esparta</t>
         </is>
       </c>
-      <c r="G191" s="7" t="n">
+      <c r="G191" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="H191" s="7" t="n">
+      <c r="H191" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="I191" s="7" t="n">
+      <c r="I191" s="5" t="n">
         <v>1927</v>
       </c>
       <c r="J191" s="4" t="inlineStr">
@@ -9267,13 +9329,13 @@
           <t>Estado Nueva Esparta</t>
         </is>
       </c>
-      <c r="G192" s="7" t="n">
+      <c r="G192" s="5" t="n">
         <v>78</v>
       </c>
-      <c r="H192" s="7" t="n">
+      <c r="H192" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="I192" s="7" t="n">
+      <c r="I192" s="5" t="n">
         <v>807</v>
       </c>
       <c r="J192" s="4" t="inlineStr">
@@ -9314,13 +9376,13 @@
           <t>Indice de Masculinidad ENT</t>
         </is>
       </c>
-      <c r="G193" s="7" t="n">
+      <c r="G193" s="5" t="n">
         <v>86</v>
       </c>
-      <c r="H193" s="7" t="n">
+      <c r="H193" s="5" t="n">
         <v>55</v>
       </c>
-      <c r="I193" s="7" t="n">
+      <c r="I193" s="5" t="n">
         <v>4159</v>
       </c>
       <c r="J193" s="4" t="inlineStr">
@@ -9361,13 +9423,13 @@
           <t>Estado Nueva Esparta</t>
         </is>
       </c>
-      <c r="G194" s="7" t="n">
+      <c r="G194" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="H194" s="7" t="n">
+      <c r="H194" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="I194" s="7" t="n">
+      <c r="I194" s="5" t="n">
         <v>1927</v>
       </c>
       <c r="J194" s="4" t="inlineStr">
@@ -9408,13 +9470,13 @@
           <t>n_CEN</t>
         </is>
       </c>
-      <c r="G195" s="7" t="n">
+      <c r="G195" s="5" t="n">
         <v>69</v>
       </c>
-      <c r="H195" s="7" t="n">
+      <c r="H195" s="5" t="n">
         <v>77</v>
       </c>
-      <c r="I195" s="7" t="n">
+      <c r="I195" s="5" t="n">
         <v>5245</v>
       </c>
       <c r="J195" s="4" t="inlineStr">
@@ -9455,13 +9517,13 @@
           <t>Estado Portuguesa</t>
         </is>
       </c>
-      <c r="G196" s="7" t="n">
+      <c r="G196" s="5" t="n">
         <v>57</v>
       </c>
-      <c r="H196" s="7" t="n">
+      <c r="H196" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="I196" s="7" t="n">
+      <c r="I196" s="5" t="n">
         <v>2395</v>
       </c>
       <c r="J196" s="4" t="inlineStr">
@@ -9502,13 +9564,13 @@
           <t>Estado Portuguesa</t>
         </is>
       </c>
-      <c r="G197" s="7" t="n">
+      <c r="G197" s="5" t="n">
         <v>78</v>
       </c>
-      <c r="H197" s="7" t="n">
+      <c r="H197" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="I197" s="7" t="n">
+      <c r="I197" s="5" t="n">
         <v>807</v>
       </c>
       <c r="J197" s="4" t="inlineStr">
@@ -9549,13 +9611,13 @@
           <t>Estado Portuguesa</t>
         </is>
       </c>
-      <c r="G198" s="7" t="n">
+      <c r="G198" s="5" t="n">
         <v>57</v>
       </c>
-      <c r="H198" s="7" t="n">
+      <c r="H198" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="I198" s="7" t="n">
+      <c r="I198" s="5" t="n">
         <v>2395</v>
       </c>
       <c r="J198" s="4" t="inlineStr">
@@ -9596,13 +9658,13 @@
           <t>n_CEN</t>
         </is>
       </c>
-      <c r="G199" s="7" t="n">
+      <c r="G199" s="5" t="n">
         <v>1600</v>
       </c>
-      <c r="H199" s="7" t="n">
+      <c r="H199" s="5" t="n">
         <v>77</v>
       </c>
-      <c r="I199" s="7" t="n">
+      <c r="I199" s="5" t="n">
         <v>121601</v>
       </c>
       <c r="J199" s="4" t="inlineStr">
@@ -9643,13 +9705,13 @@
           <t>Estado Sucre</t>
         </is>
       </c>
-      <c r="G200" s="7" t="n">
+      <c r="G200" s="5" t="n">
         <v>60</v>
       </c>
-      <c r="H200" s="7" t="n">
+      <c r="H200" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="I200" s="7" t="n">
+      <c r="I200" s="5" t="n">
         <v>2551</v>
       </c>
       <c r="J200" s="4" t="inlineStr">
@@ -9690,13 +9752,13 @@
           <t>Estado Sucre</t>
         </is>
       </c>
-      <c r="G201" s="7" t="n">
+      <c r="G201" s="5" t="n">
         <v>78</v>
       </c>
-      <c r="H201" s="7" t="n">
+      <c r="H201" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="I201" s="7" t="n">
+      <c r="I201" s="5" t="n">
         <v>807</v>
       </c>
       <c r="J201" s="4" t="inlineStr">
@@ -9737,13 +9799,13 @@
           <t>Estado Sucre</t>
         </is>
       </c>
-      <c r="G202" s="7" t="n">
+      <c r="G202" s="5" t="n">
         <v>60</v>
       </c>
-      <c r="H202" s="7" t="n">
+      <c r="H202" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="I202" s="7" t="n">
+      <c r="I202" s="5" t="n">
         <v>2551</v>
       </c>
       <c r="J202" s="4" t="inlineStr">
@@ -9784,13 +9846,13 @@
           <t>n_CEN</t>
         </is>
       </c>
-      <c r="G203" s="7" t="n">
+      <c r="G203" s="5" t="n">
         <v>874</v>
       </c>
-      <c r="H203" s="7" t="n">
+      <c r="H203" s="5" t="n">
         <v>77</v>
       </c>
-      <c r="I203" s="7" t="n">
+      <c r="I203" s="5" t="n">
         <v>66431</v>
       </c>
       <c r="J203" s="4" t="inlineStr">
@@ -9831,13 +9893,13 @@
           <t>Estado Táchira</t>
         </is>
       </c>
-      <c r="G204" s="7" t="n">
+      <c r="G204" s="5" t="n">
         <v>78</v>
       </c>
-      <c r="H204" s="7" t="n">
+      <c r="H204" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="I204" s="7" t="n">
+      <c r="I204" s="5" t="n">
         <v>807</v>
       </c>
       <c r="J204" s="4" t="inlineStr">
@@ -9878,13 +9940,13 @@
           <t>Estado Trujillo</t>
         </is>
       </c>
-      <c r="G205" s="7" t="n">
+      <c r="G205" s="5" t="n">
         <v>75</v>
       </c>
-      <c r="H205" s="7" t="n">
+      <c r="H205" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="I205" s="7" t="n">
+      <c r="I205" s="5" t="n">
         <v>3331</v>
       </c>
       <c r="J205" s="4" t="inlineStr">
@@ -9925,13 +9987,13 @@
           <t>Estado Trujillo</t>
         </is>
       </c>
-      <c r="G206" s="7" t="n">
+      <c r="G206" s="5" t="n">
         <v>78</v>
       </c>
-      <c r="H206" s="7" t="n">
+      <c r="H206" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="I206" s="7" t="n">
+      <c r="I206" s="5" t="n">
         <v>807</v>
       </c>
       <c r="J206" s="4" t="inlineStr">
@@ -9972,13 +10034,13 @@
           <t>Estado Trujillo</t>
         </is>
       </c>
-      <c r="G207" s="7" t="n">
+      <c r="G207" s="5" t="n">
         <v>75</v>
       </c>
-      <c r="H207" s="7" t="n">
+      <c r="H207" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="I207" s="7" t="n">
+      <c r="I207" s="5" t="n">
         <v>3331</v>
       </c>
       <c r="J207" s="4" t="inlineStr">
@@ -10019,13 +10081,13 @@
           <t>n_CEN</t>
         </is>
       </c>
-      <c r="G208" s="7" t="n">
+      <c r="G208" s="5" t="n">
         <v>1527</v>
       </c>
-      <c r="H208" s="7" t="n">
+      <c r="H208" s="5" t="n">
         <v>77</v>
       </c>
-      <c r="I208" s="7" t="n">
+      <c r="I208" s="5" t="n">
         <v>116054</v>
       </c>
       <c r="J208" s="4" t="inlineStr">
@@ -10066,13 +10128,13 @@
           <t>Estado Táchira</t>
         </is>
       </c>
-      <c r="G209" s="7" t="n">
+      <c r="G209" s="5" t="n">
         <v>102</v>
       </c>
-      <c r="H209" s="7" t="n">
+      <c r="H209" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="I209" s="7" t="n">
+      <c r="I209" s="5" t="n">
         <v>4735</v>
       </c>
       <c r="J209" s="4" t="inlineStr">
@@ -10113,13 +10175,13 @@
           <t>Estado Táchira</t>
         </is>
       </c>
-      <c r="G210" s="7" t="n">
+      <c r="G210" s="5" t="n">
         <v>102</v>
       </c>
-      <c r="H210" s="7" t="n">
+      <c r="H210" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="I210" s="7" t="n">
+      <c r="I210" s="5" t="n">
         <v>4735</v>
       </c>
       <c r="J210" s="4" t="inlineStr">
@@ -10160,13 +10222,13 @@
           <t>n_CEN</t>
         </is>
       </c>
-      <c r="G211" s="7" t="n">
+      <c r="G211" s="5" t="n">
         <v>1761</v>
       </c>
-      <c r="H211" s="7" t="n">
+      <c r="H211" s="5" t="n">
         <v>77</v>
       </c>
-      <c r="I211" s="7" t="n">
+      <c r="I211" s="5" t="n">
         <v>133843</v>
       </c>
       <c r="J211" s="4" t="inlineStr">
@@ -10207,13 +10269,13 @@
           <t>Estado Yaracuy</t>
         </is>
       </c>
-      <c r="G212" s="7" t="n">
+      <c r="G212" s="5" t="n">
         <v>57</v>
       </c>
-      <c r="H212" s="7" t="n">
+      <c r="H212" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="I212" s="7" t="n">
+      <c r="I212" s="5" t="n">
         <v>2395</v>
       </c>
       <c r="J212" s="4" t="inlineStr">
@@ -10254,13 +10316,13 @@
           <t>Estado Yaracuy</t>
         </is>
       </c>
-      <c r="G213" s="7" t="n">
+      <c r="G213" s="5" t="n">
         <v>78</v>
       </c>
-      <c r="H213" s="7" t="n">
+      <c r="H213" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="I213" s="7" t="n">
+      <c r="I213" s="5" t="n">
         <v>807</v>
       </c>
       <c r="J213" s="4" t="inlineStr">
@@ -10301,13 +10363,13 @@
           <t>Estado Yaracuy</t>
         </is>
       </c>
-      <c r="G214" s="7" t="n">
+      <c r="G214" s="5" t="n">
         <v>57</v>
       </c>
-      <c r="H214" s="7" t="n">
+      <c r="H214" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="I214" s="7" t="n">
+      <c r="I214" s="5" t="n">
         <v>2395</v>
       </c>
       <c r="J214" s="4" t="inlineStr">
@@ -10348,13 +10410,13 @@
           <t>n_CEN</t>
         </is>
       </c>
-      <c r="G215" s="7" t="n">
+      <c r="G215" s="5" t="n">
         <v>958</v>
       </c>
-      <c r="H215" s="7" t="n">
+      <c r="H215" s="5" t="n">
         <v>77</v>
       </c>
-      <c r="I215" s="7" t="n">
+      <c r="I215" s="5" t="n">
         <v>72810</v>
       </c>
       <c r="J215" s="4" t="inlineStr">
@@ -10395,13 +10457,13 @@
           <t>Estado Zulia</t>
         </is>
       </c>
-      <c r="G216" s="7" t="n">
+      <c r="G216" s="5" t="n">
         <v>78</v>
       </c>
-      <c r="H216" s="7" t="n">
+      <c r="H216" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="I216" s="7" t="n">
+      <c r="I216" s="5" t="n">
         <v>3487</v>
       </c>
       <c r="J216" s="4" t="inlineStr">
@@ -10442,13 +10504,13 @@
           <t>Estado Zulia</t>
         </is>
       </c>
-      <c r="G217" s="7" t="n">
+      <c r="G217" s="5" t="n">
         <v>78</v>
       </c>
-      <c r="H217" s="7" t="n">
+      <c r="H217" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="I217" s="7" t="n">
+      <c r="I217" s="5" t="n">
         <v>807</v>
       </c>
       <c r="J217" s="4" t="inlineStr">
@@ -10489,13 +10551,13 @@
           <t>Estado Zulia</t>
         </is>
       </c>
-      <c r="G218" s="7" t="n">
+      <c r="G218" s="5" t="n">
         <v>78</v>
       </c>
-      <c r="H218" s="7" t="n">
+      <c r="H218" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="I218" s="7" t="n">
+      <c r="I218" s="5" t="n">
         <v>3487</v>
       </c>
       <c r="J218" s="4" t="inlineStr">
@@ -10536,13 +10598,13 @@
           <t>n_CEN</t>
         </is>
       </c>
-      <c r="G219" s="7" t="n">
+      <c r="G219" s="5" t="n">
         <v>4825</v>
       </c>
-      <c r="H219" s="7" t="n">
+      <c r="H219" s="5" t="n">
         <v>77</v>
       </c>
-      <c r="I219" s="7" t="n">
+      <c r="I219" s="5" t="n">
         <v>366769</v>
       </c>
       <c r="J219" s="4" t="inlineStr">
@@ -10583,13 +10645,13 @@
           <t>Edad Simple</t>
         </is>
       </c>
-      <c r="G220" s="7" t="n">
+      <c r="G220" s="5" t="n">
         <v>318</v>
       </c>
-      <c r="H220" s="7" t="n">
+      <c r="H220" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="I220" s="7" t="n">
+      <c r="I220" s="5" t="n">
         <v>3687</v>
       </c>
       <c r="J220" s="4" t="inlineStr">
@@ -10630,13 +10692,13 @@
           <t>Esperanza de Vida</t>
         </is>
       </c>
-      <c r="G221" s="7" t="n">
+      <c r="G221" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="H221" s="7" t="n">
+      <c r="H221" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="I221" s="7" t="n">
+      <c r="I221" s="5" t="n">
         <v>217</v>
       </c>
       <c r="J221" s="4" t="inlineStr">
@@ -10677,13 +10739,13 @@
           <t>Resumen Entidad</t>
         </is>
       </c>
-      <c r="G222" s="7" t="n">
+      <c r="G222" s="5" t="n">
         <v>93</v>
       </c>
-      <c r="H222" s="7" t="n">
+      <c r="H222" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="I222" s="7" t="n">
+      <c r="I222" s="5" t="n">
         <v>4113</v>
       </c>
       <c r="J222" s="4" t="inlineStr">
@@ -10724,13 +10786,13 @@
           <t>n_CEN</t>
         </is>
       </c>
-      <c r="G223" s="7" t="n">
+      <c r="G223" s="5" t="n">
         <v>671</v>
       </c>
-      <c r="H223" s="7" t="n">
+      <c r="H223" s="5" t="n">
         <v>77</v>
       </c>
-      <c r="I223" s="7" t="n">
+      <c r="I223" s="5" t="n">
         <v>50997</v>
       </c>
       <c r="J223" s="4" t="inlineStr">
@@ -10771,13 +10833,13 @@
           <t>Estado Aragua</t>
         </is>
       </c>
-      <c r="G224" s="7" t="n">
+      <c r="G224" s="5" t="n">
         <v>69</v>
       </c>
-      <c r="H224" s="7" t="n">
+      <c r="H224" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="I224" s="7" t="n">
+      <c r="I224" s="5" t="n">
         <v>3019</v>
       </c>
       <c r="J224" s="4" t="inlineStr">
@@ -10818,13 +10880,13 @@
           <t>Estado Aragua</t>
         </is>
       </c>
-      <c r="G225" s="7" t="n">
+      <c r="G225" s="5" t="n">
         <v>78</v>
       </c>
-      <c r="H225" s="7" t="n">
+      <c r="H225" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="I225" s="7" t="n">
+      <c r="I225" s="5" t="n">
         <v>807</v>
       </c>
       <c r="J225" s="4" t="inlineStr">
@@ -10865,13 +10927,13 @@
           <t>Estado Aragua</t>
         </is>
       </c>
-      <c r="G226" s="7" t="n">
+      <c r="G226" s="5" t="n">
         <v>69</v>
       </c>
-      <c r="H226" s="7" t="n">
+      <c r="H226" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="I226" s="7" t="n">
+      <c r="I226" s="5" t="n">
         <v>3019</v>
       </c>
       <c r="J226" s="4" t="inlineStr">
@@ -10918,19 +10980,19 @@
     <row r="4" ht="16" customHeight="1"/>
     <row r="5" ht="8" customHeight="1"/>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>Campo</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Organización</t>
         </is>
@@ -10942,7 +11004,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Dataset</t>
         </is>
@@ -10954,7 +11016,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Fecha generación</t>
         </is>
@@ -10966,7 +11028,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
@@ -10978,7 +11040,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>URL portal</t>
         </is>
@@ -10990,7 +11052,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>País</t>
         </is>
@@ -11002,57 +11064,57 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>Número de recursos</t>
         </is>
       </c>
-      <c r="B13" s="7" t="n">
+      <c r="B13" s="5" t="n">
         <v>323</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>Recursos tabulares</t>
         </is>
       </c>
-      <c r="B14" s="7" t="n">
+      <c r="B14" s="5" t="n">
         <v>204</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>Documentos</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n">
+      <c r="B15" s="5" t="n">
         <v>119</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>Hojas extraídas</t>
         </is>
       </c>
-      <c r="B16" s="7" t="n">
+      <c r="B16" s="5" t="n">
         <v>220</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>Celdas con valor extraídas</t>
         </is>
       </c>
-      <c r="B17" s="7" t="n">
+      <c r="B17" s="5" t="n">
         <v>2980320</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>Archivo valores CSV.GZ</t>
         </is>

--- a/assets/data/ine/excel/ove_ine_venezuela_indice_hojas.xlsx
+++ b/assets/data/ine/excel/ove_ine_venezuela_indice_hojas.xlsx
@@ -11023,7 +11023,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>

--- a/assets/data/ine/excel/ove_ine_venezuela_indice_hojas.xlsx
+++ b/assets/data/ine/excel/ove_ine_venezuela_indice_hojas.xlsx
@@ -11023,7 +11023,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -11070,7 +11070,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="14">
@@ -11090,7 +11090,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">

--- a/assets/data/ine/excel/ove_ine_venezuela_indice_hojas.xlsx
+++ b/assets/data/ine/excel/ove_ine_venezuela_indice_hojas.xlsx
@@ -11023,7 +11023,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
@@ -11070,7 +11070,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="14">
@@ -11090,7 +11090,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16">

--- a/assets/data/ine/excel/ove_ine_venezuela_indice_hojas.xlsx
+++ b/assets/data/ine/excel/ove_ine_venezuela_indice_hojas.xlsx
@@ -11023,7 +11023,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
@@ -11070,7 +11070,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="14">
@@ -11090,7 +11090,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="16">

--- a/assets/data/ine/excel/ove_ine_venezuela_indice_hojas.xlsx
+++ b/assets/data/ine/excel/ove_ine_venezuela_indice_hojas.xlsx
@@ -11023,7 +11023,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
@@ -11070,7 +11070,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="14">
@@ -11090,7 +11090,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16">

--- a/assets/data/ine/excel/ove_ine_venezuela_indice_hojas.xlsx
+++ b/assets/data/ine/excel/ove_ine_venezuela_indice_hojas.xlsx
@@ -11023,7 +11023,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
@@ -11070,7 +11070,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>327</v>
+        <v>334</v>
       </c>
     </row>
     <row r="14">
@@ -11090,7 +11090,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16">
